--- a/PANAMA_SIRKULER/PANAMA_Sirkuler_Analizi_Turkce.xlsx
+++ b/PANAMA_SIRKULER/PANAMA_Sirkuler_Analizi_Turkce.xlsx
@@ -413,33 +413,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Dosya Adı</t>
+          <t>Filename</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Konu (İngilizce)</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Konu (TÜRKÇE)</t>
+          <t>Subject_EN</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Özet (İngilizce)</t>
+          <t>Subject_TR</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Özet (TÜRKÇE)</t>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Summary_EN</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Summary_TR</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Recommendations_TR</t>
         </is>
       </c>
     </row>
@@ -449,30 +464,37 @@
           <t>Circular-DGGM-007-Version-01-Formularios-originales-de-los-titulos-y-documentacion-tecnica-de-la-gente-de-mar-aprobados-por-la-AMP-ES-IN.pdf</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
         <is>
           <t>DGGM-007</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>DGGM-007</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>of this Circular is to communicate to the users of the Panamanian Registry, the 
 original forms of certificates and technical documentation for seafarers approved by the 
 Panama Maritime Authority....</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına iletilmek üzere, 
 tarafından onaylanan denizcilere yönelik sertifikaların ve teknik belgelerin orijinal formları 
 Panama Denizcilik Otoritesi....</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -480,17 +502,19 @@
           <t>Circular-DGGM-008-Version-05-Adopcion-y-reglamentacion-del-Convenio-STCW´78-enmendado-y-su-Codigo-de-Formacion-ES-IN.pdf</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>DGGM-008</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>DGGM-008</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>of this Circular is to communicate to the users of the Panamanian Registry, the 
 regulations of the Republic of Panama and the Panama Maritime Authority (PMA) by means of 
@@ -500,7 +524,7 @@
 adopted and regulated....</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına iletilmek üzere, 
 Panama Cumhuriyeti ve Panama Denizcilik Otoritesi'nin (PMA) düzenlemeleri aracılığıyla 
@@ -510,6 +534,11 @@
 kabul edilmiş ve düzenlenmiştir....</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -517,24 +546,31 @@
           <t>Circular-DGPIMA-001-DECCP-2026.pdf</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>FECHA:</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>- Fecha:</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bulunamadı...</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Bulunamadı...</t>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>This circular defines the regulations, guidelines, and compliance requirements regarding FECHA:....</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bu genelge FECHA'ya ilişkin düzenlemeleri, yönergeleri ve uyumluluk gerekliliklerini tanımlar:....</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
         </is>
       </c>
     </row>
@@ -544,24 +580,31 @@
           <t>Circular-DGPIMA-002-DECCP-2026.pdf</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
         <is>
           <t>FECHA:</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>- Fecha:</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Bulunamadı...</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bulunamadı...</t>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>This circular defines the regulations, guidelines, and compliance requirements regarding FECHA:....</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bu genelge FECHA'ya ilişkin düzenlemeleri, yönergeleri ve uyumluluk gerekliliklerini tanımlar:....</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
         </is>
       </c>
     </row>
@@ -571,17 +614,19 @@
           <t>Circular-No.-DGGM-050-V01-Informacion-de-contacto-de-las-unidades-administrativas-de-la-DGGM-de-la-AMP.pdf</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
         <is>
           <t>DGGM-050</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>DGGM-050</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>of this Circular is to communicate to the users of the Panamanian Registry, the 
 contact information for the administrative units of the General Directorate of Seafarers of the 
@@ -593,7 +638,7 @@
 Certification Dep...</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına iletilmek üzere, 
 Gemi Adamları Genel Müdürlüğü idari birimlerinin iletişim bilgileri 
@@ -607,24 +652,231 @@
 doğrulama@am...</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>MMC-131-31-03-2022-1.pdf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MMC-131</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MMC-131</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>of this Merchant Marine Circular is to serve as guidance regarding the 
+amendments to the SOLAS Convention and to the new Chapters regarding Maritime 
+Security and the ISPS Code....</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, aşağıdaki hususlara ilişkin rehberlik görevi görecektir: 
+SOLAS Sözleşmesinde ve Denizcilikle İlgili Yeni Bölümlerde Değişiklikler 
+Güvenlik ve ISPS Kodu...</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MMC-195-LRIT-23-11-2020.pdf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MMC-195</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MMC-195</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>This circular defines the regulations, guidelines, and compliance requirements regarding MMC-195....</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bu sirküler MMC-195'e ilişkin düzenlemeleri, yönergeleri ve uyumluluk gerekliliklerini tanımlar....</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MMC-206-27-07-2018-PROTECCION-ISPS.pdf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MMC-206</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MMC-206</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>of this Circular is to update the responsibilities of the Company Security Officer (CSO) like a person 
+designated by the Company to ensure that a Ships Security Assessment (SSA) is carried out; that a Ship Security Plan (SSP) 
+is developed and submitted for approval, thereafter implemented and maintained, and liaison with Port Facility Security 
+Officer (PFSO) and the Ship Security Officer (SSO)....</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı Şirket Güvenlik Görevlisinin (CSO) bir kişi gibi sorumluluklarını güncellemektir. 
+Şirket tarafından Gemi Güvenlik Değerlendirmesinin (SSA) yürütülmesini sağlamak üzere belirlenen; bir Gemi Güvenlik Planının (SSP) 
+geliştirilir ve onaya sunulur, daha sonra uygulanır ve sürdürülür ve Liman Tesisi Güvenliği ile irtibat sağlanır. 
+Zabit (PFSO) ve Gemi Güvenlik Zabiti (SSO)....</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MMC-337-2019-June-2019-Protecci%C3%B3n-ISPS2.pdf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MMC-337</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MMC-337</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform all the users of the Panamanian Registry the following instructions for the 
+payment of the Continuous Synopsis Record (CSR) and International Ship Security Certificate (ISSC): 
+a) 
+If the Payment of the Continuous Synopsis Record (CSR) or International Ship Security Certificate (ISSC) is 
+request in our Head Office in Panama or through any General Panamanian Consulate that is not mentioned 
+below, those certificates will be sent by mail by the Head Office in Pana...</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili'nin tüm kullanıcılarına aşağıdaki talimatlar hakkında bilgi vermektir: 
+Sürekli Özet Kaydının (CSR) ve Uluslararası Gemi Güvenlik Sertifikasının (ISSC) ödenmesi: 
+a) 
+Sürekli Özet Kaydının (CSR) veya Uluslararası Gemi Güvenlik Sertifikasının (ISSC) Ödemesi 
+Panama'daki Merkez Ofisimizden veya adı geçmeyen herhangi bir Panama Genel Konsolosluğu aracılığıyla talepte bulunabilirsiniz. 
+aşağıda, bu sertifikalar Pana'daki Merkez Ofis tarafından posta yoluyla gönderilecektir...</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MMC-354-.pdf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MMC-354</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MMC-354</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this Merchant Marine Circular is to inform that the Facilitation 
+Committee (FAL) and Maritime Safety Committee (MSC) of the International 
+Maritime Organization approved the Guidelines on Maritime Cyber Risk 
+Management thorough MSC-FLA.1/Circ.3 as well as the Resolution MSC.428(98) 
+Maritime Cyber Risk Management in Safety Management Systems (SMS) on June 
+16, 2017 (for both documents  visit Maritime Security link, IMO Documents)....</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.1 Bu Ticari Denizcilik Genelgesinin amacı, Kolaylaştırmanın 
+Uluslararası Komite (FAL) ve Deniz Güvenliği Komitesi (MSC) 
+Denizcilik Örgütü, Denizcilik Siber Riskine İlişkin Kılavuz'u onayladı 
+MSC-FLA.1/Circ.3 ve MSC.428(98) Çözümü ile kapsamlı yönetim 
+Haziran'da Emniyet Yönetim Sistemlerinde (SMS) Denizcilik Siber Risk Yönetimi 
+16, 2017 (her iki belge için Deniz Güvenliği bağlantısını, IMO Belgelerini ziyaret edin)....</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Resolucion-ADM-No.-123-2017-de-28-de-julio-de-2017-ES-IN.pdf</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
         <is>
           <t>s.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>S.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>s of Article XII(1)(a)(v) of the 
 Convention, to transmit certified copies of the present resolution and the text of the 
@@ -639,7 +891,7 @@
 AMENDMENTS TO ...</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Madde XII(1)(a)(v)'nin 
 Mevcut kararın onaylı kopyalarının ve karar metninin iletilmesi 
@@ -655,24 +907,31 @@
 EĞİTİM, SERTİFİKASYON VE...</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Resolucion-ADM-No.-232-2016-de-29-de-diciembre-de-2016-ES-IN.pdf</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
         <is>
           <t>to the International Code of safety for</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Uluslararası Güvenlik Koduna göre</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
         <is>
           <t>s of article XII(1)(a)(v) of 
 the Convention, to transmit certified copies of the present resolution and the text of 
@@ -688,7 +947,7 @@
 STAND...</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>XII(1)(a)(v) maddesinin hükümleri 
 Sözleşmenin, mevcut kararın onaylı kopyalarını ve metnini iletmesini talep ediyorum. 
@@ -704,24 +963,31 @@
 EĞİTİM, SERTİFİKASYON VE VARDİYA TUTMA STANDARTLARI ...</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Resolucion-ADM-No.-249-2021-de-12-de-noviembre-de-2021-ES-IN.pdf</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
         <is>
           <t>to the International Code of Safety</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Uluslararası Güvenlik Koduna</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
         <is>
           <t>, and keep the mandatory instruments of the 
 International Maritime Organization (IMO) updated, of which the Republic of Panama is 
@@ -733,7 +999,7 @@
 article 186 of Law No. 57 of August...</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>ve zorunlu enstrümanları saklayın 
 Panama Cumhuriyeti'nin de dahil olduğu Uluslararası Denizcilik Örgütü (IMO) güncellendi 
@@ -744,24 +1010,31 @@
 Tarafından değiştirilen 10 Şubat 1998 tarih ve 7 sayılı Kanun Hükmünde Kararname hükümleri uya...</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Resolucion-ADM-No.-276-2015-de-28-de-diciembre-de-2015-ES-IN.pdf</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
         <is>
           <t>s.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>S.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
         <is>
           <t>of regulation I/16 the areas that shall be subject to audit are 
 indicated in the table below: 
@@ -786,7 +1059,7 @@
 demonstrat...</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Yönetmelik I/16'da denetime tabi olacak alanlar şunlardır: 
 aşağıdaki tabloda belirtilmiştir: 
@@ -814,24 +1087,31 @@
 SONRAKİ RAPO...</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Resolucion-ADM-No.-302-2023-de-29-de-diciembre-de-2023-ES-IN.pdf</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
         <is>
           <t>to the International Code of Safety</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Uluslararası Güvenlik Koduna</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>, and keeping the mandatory instruments of the 
 International Maritime Organization (IMO) updated, to which the Republic of Panama is 
@@ -843,7 +1123,7 @@
 by Article 186 of Law No. 57 of A...</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>ve zorunlu enstrümanların bulundurulması 
 Panama Cumhuriyeti'nin üye olduğu Uluslararası Denizcilik Örgütü (IMO) güncellendi 
@@ -855,24 +1135,31 @@
 6 Ağustos 2008 tarih ve 57 sayı...</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Resolucion-J.D.-No.-053-2021-de-2-de-agosto-de-2021-ES-IN.pdf</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
         <is>
           <t>MSC.1/Circ.1163 (latest revision) of the</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>MSC.1/Circ.1163 (en son revizyon)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>of meeting the international standards, and 
 maintain the efficiency and competitiveness of the Panama shipping registry and the seafarers. 
@@ -882,7 +1169,7 @@
 profitability of the maritime sector and the development of its human res...</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Uluslararası standartların karşılanması ve 
 Panama denizcilik sicilinin ve denizcilerin verimliliğini ve rekabet gücünü korumak. 
@@ -893,24 +1180,31 @@
 Kurumun organizasyonu ve oranların ...</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Resolucion-J.D.-No.-076-2020-de-8-de-octubre-de-2020-ES-IN.pdf</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
         <is>
           <t>MSC.1/Circ.1163 (last revision) of</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>MSC.1/Circ.1163 (son revizyon)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
         <is>
           <t>s of these Regulations and unless otherwise expressly 
 stated, the following definitions shall apply: 
@@ -922,7 +1216,7 @@
 standards of seafarers, in according t...</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Bu Yönetmeliklerin hükümleri ve aksi açıkça belirtilmediği sürece 
 belirtilmesi durumunda aşağıdaki tanımlar geçerli olacaktır: 
@@ -934,169 +1228,9 @@
 1978 STCW...</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MMC-131-31-03-2022-1.pdf</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MMC-131</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MMC-131</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>of this Merchant Marine Circular is to serve as guidance regarding the 
-amendments to the SOLAS Convention and to the new Chapters regarding Maritime 
-Security and the ISPS Code....</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Bu Ticari Denizcilik Genelgesi, aşağıdaki hususlara ilişkin rehberlik görevi görecektir: 
-SOLAS Sözleşmesinde ve Denizcilikle İlgili Yeni Bölümlerde Değişiklikler 
-Güvenlik ve ISPS Kodu...</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MMC-195-LRIT-23-11-2020.pdf</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MMC-195</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MMC-195</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>This circular defines the regulations, guidelines, and compliance requirements regarding MMC-195....</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Bu sirküler MMC-195'e ilişkin düzenlemeleri, yönergeleri ve uyumluluk gerekliliklerini tanımlar....</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MMC-337-2019-June-2019-Protecci%C3%B3n-ISPS2.pdf</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MMC-337</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MMC-337</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>of this Circular is to inform all the users of the Panamanian Registry the following instructions for the 
-payment of the Continuous Synopsis Record (CSR) and International Ship Security Certificate (ISSC): 
-a) 
-If the Payment of the Continuous Synopsis Record (CSR) or International Ship Security Certificate (ISSC) is 
-request in our Head Office in Panama or through any General Panamanian Consulate that is not mentioned 
-below, those certificates will be sent by mail by the Head Office in Pana...</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Bu Genelgenin amacı, Panama Sicili'nin tüm kullanıcılarına aşağıdaki talimatlar hakkında bilgi vermektir: 
-Sürekli Özet Kaydının (CSR) ve Uluslararası Gemi Güvenlik Sertifikasının (ISSC) ödenmesi: 
-a) 
-Sürekli Özet Kaydının (CSR) veya Uluslararası Gemi Güvenlik Sertifikasının (ISSC) Ödemesi 
-Panama'daki Merkez Ofisimizden veya adı geçmeyen herhangi bir Panama Genel Konsolosluğu aracılığıyla talepte bulunabilirsiniz. 
-aşağıda, bu sertifikalar Pana'daki Merkez Ofis tarafından posta yoluyla gönderilecektir...</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MMC-206-27-07-2018-PROTECCION-ISPS.pdf</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MMC-206</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MMC-206</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>of this Circular is to update the responsibilities of the Company Security Officer (CSO) like a person 
-designated by the Company to ensure that a Ships Security Assessment (SSA) is carried out; that a Ship Security Plan (SSP) 
-is developed and submitted for approval, thereafter implemented and maintained, and liaison with Port Facility Security 
-Officer (PFSO) and the Ship Security Officer (SSO)....</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Bu Genelgenin amacı Şirket Güvenlik Görevlisinin (CSO) bir kişi gibi sorumluluklarını güncellemektir. 
-Şirket tarafından Gemi Güvenlik Değerlendirmesinin (SSA) yürütülmesini sağlamak üzere belirlenen; bir Gemi Güvenlik Planının (SSP) 
-geliştirilir ve onaya sunulur, daha sonra uygulanır ve sürdürülür ve Liman Tesisi Güvenliği ile irtibat sağlanır. 
-Zabit (PFSO) ve Gemi Güvenlik Zabiti (SSO)....</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MMC-354-.pdf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>MMC-354</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MMC-354</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1.1 The purpose of this Merchant Marine Circular is to inform that the Facilitation 
-Committee (FAL) and Maritime Safety Committee (MSC) of the International 
-Maritime Organization approved the Guidelines on Maritime Cyber Risk 
-Management thorough MSC-FLA.1/Circ.3 as well as the Resolution MSC.428(98) 
-Maritime Cyber Risk Management in Safety Management Systems (SMS) on June 
-16, 2017 (for both documents  visit Maritime Security link, IMO Documents)....</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1.1 Bu Ticari Denizcilik Genelgesinin amacı, Kolaylaştırmanın 
-Uluslararası Komite (FAL) ve Deniz Güvenliği Komitesi (MSC) 
-Denizcilik Örgütü, Denizcilik Siber Riskine İlişkin Kılavuz'u onayladı 
-MSC-FLA.1/Circ.3 ve MSC.428(98) Çözümü ile kapsamlı yönetim 
-Haziran'da Emniyet Yönetim Sistemlerinde (SMS) Denizcilik Siber Risk Yönetimi 
-16, 2017 (her iki belge için Deniz Güvenliği bağlantısını, IMO Belgelerini ziyaret edin)....</t>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1. İlgili genelgeyi gemideki sirküler klasörüne ekleyerek zabitlere tebliğ edin. 2. Genelgede belirtilen teknik şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
         </is>
       </c>
     </row>

--- a/PANAMA_SIRKULER/PANAMA_Sirkuler_Analizi_Turkce.xlsx
+++ b/PANAMA_SIRKULER/PANAMA_Sirkuler_Analizi_Turkce.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1234,6 +1234,8290 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MMC-374-05-06-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MMC-374</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MMC-374</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>To establish and disseminate the list of national and foreign companies that are duly 
+registered and authorized by the Flag State Inspection Section of the Navigation and 
+Maritime Safety Department, under the General Directorate of Merchant Marine, to act 
+as the exclusive representatives of Flag ...</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Deniz Ticareti Genel Müdürlüğü Seyir ve Deniz Emniyeti Dairesi Başkanlığı Bayrak Devleti Denetleme Dairesi Başkanlığı tarafından usulüne uygun olarak tescil edilen ve Bayrak Devleti'nin münhasır temsilcisi olarak görev yapmak üzere yetkilendirilen yerli ve yabancı şirketlerin listesini oluşturmak ve dağıtmak.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-374-05-06-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MMC-183-rev-dccm-5-6-2026-limpio-1.pdf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2.1 The purpose of this circular is to establish the requirements for the issuance of the Continuous Synopsis 
+Record (CSR), as well as the Administration's policies regarding the information that the CSR must contain. 
+3. SCOPE AND APPLICABILITY: 
+3.1.1 This Merchant Marine Circular applies to ...</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2.1 Bu sirkülerin amacı, Sürekli Özet Kaydının (CSR) yayınlanmasına ilişkin gereklilikleri ve ayrıca CSR'nin içermesi gereken bilgilere ilişkin İdare politikalarını belirlemektir.    3. KAPSAM VE UYGULANABİLİRLİK: 3.1.1 Bu Ticari Denizcilik Genelgesi aşağıdakiler için geçerlidir:</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-183-rev-dccm-5-6-2026-limpio-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MMC-245-1-06-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MMC-245</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MMC-245</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>The purpose of this circular is to list the private security companies authorized by the PMA 
+to provide the service of armed personnel on board Panamanian-flagged vessels, as well 
+as the recommendations and policies that those companies must comply with during their 
+accreditation. 
+3. Scope: 
+ ...</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bu genelgenin amacı, Panama bayraklı gemilerde silahlı personele hizmet vermek üzere PMA tarafından yetkilendirilen özel güvenlik şirketlerini ve bu şirketlerin akreditasyonları sırasında uymaları gereken tavsiye ve politikaları listelemektir.    3. Kapsam: ...</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-245-1-06-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MMC-407-WELCOME-GUIDANCE-AND-POST-REGISTRATION-06-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MMC-407</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MMC-407</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Merchant Marine Circular is to provide guidance to users of 
+Panama Ship Registry regarding the requirements applicable to vessels after their 
+registration under the Panama Ship Registry.  
+1.2. It also aims to keep stakeholders informed of the various instruments adopted...</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesinin amacı, Panama Gemi Sicili kullanıcılarına, Panama Gemi Siciline tescil edildikten sonra gemilere uygulanan gereklilikler konusunda rehberlik sağlamaktır.     1.2. Ayrıca paydaşların benimsenen çeşitli araçlar hakkında bilgilendirilmesi de amaçlanıyor...</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-407-WELCOME-GUIDANCE-AND-POST-REGISTRATION-06-05-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MMC-258-V04-MAY-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MMC-258</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MMC-258</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1.1. 
+Inform the requirements to apply for permanent authorization by this 
+Administration and also make available the list of its authorized services 
+providers. 
+1.2. 
+To remind that authorized service providers must ensure that its personnel 
+performing this work shall be certified in accordance ...</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.1.  Bu İdare tarafından kalıcı izin başvurusuna ilişkin gereklilikleri bildirin ve aynı zamanda yetkili hizmet sağlayıcılarının listesini de hazır bulundurun.  1.2.  Yetkili servis sağlayıcıların bu işi yapan personelinin standartlara uygun olarak sertifikalandırılmasını sağlamaları gerektiğini hatırlatmak isterim...</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-258-V04-MAY-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MMC-270-24-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MMC-270</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MMC-270</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>The purpose of this Merchant Marine Circular is to inform the requirements applicable to 
+fishing vessel and other ships engaged in fishing related activities registered under 
+Panama flag, according to the responsibilities of the national authorities related to this 
+issue.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bu Deniz Ticareti Genelgesinin amacı, ulusal otoritelerin bu konuya ilişkin sorumlulukları uyarınca, Panama bayrağı altında kayıtlı balıkçı tekneleri ve balıkçılıkla ilgili faaliyetlerde bulunan diğer gemiler için geçerli olan gereklilikleri bilgilendirmektir.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-270-24-04-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MMC-230-22-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MMC-230</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MMC-230</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>The purpose of this circular is to establish recommendatory measures for Panamanian-
+registered ships that transit through high-risk areas or areas where robberies and pirate attacks 
+are taking place. 
+INDEX: 
+1. Description of High-Risk Areas (HRA).</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bu genelgenin amacı, yüksek riskli bölgelerden veya soygun ve korsan saldırılarının gerçekleştiği bölgelerden geçiş yapan Panama tescilli gemiler için tavsiye niteliğinde önlemler oluşturmaktır.    DİZİN: 1. Yüksek Riskli Bölgelerin (HRA) Tanımı.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-230-22-04-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MMC-193-April-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MMC-193</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MMC-193</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular has the purpose of informing all interested parties that this 
+Administration has established through Resolution No.106-52-DGMM of September 9, 
+2024, the regulatory scheme for the approval of the voluntary use of Electronic Record 
+Books on board Panamanian vessels, as...</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Bu Deniz Ticaret Genelgesi, tüm ilgili tarafları, bu İdarenin 9 Eylül 2024 tarih ve 106-52-GİGM Kararı ile Panama gemilerinde Elektronik Kayıt Defterlerinin gönüllü kullanımının onaylanmasına yönelik düzenleyici plan oluşturduğu konusunda bilgilendirmeyi amaçlamaktadır.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-193-April-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MMC-408-Lifiting-appliances-Anchor-handling-march-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MMC-408</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MMC-408</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Merchant Marine Circular is to clarify the provisions that are to 
+the satisfaction of the Administration stipulated in Regulation 3-13 – “Lifting 
+appliances and anchor handling winches.” As well as to ensure that lifting 
+appliances and anchor handling winches fitted on Pa...</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.1. Bu Deniz Ticareti Genelgesinin amacı, Kural 3-13 – “Kaldırma donanımları ve çapa taşıma vinçleri”nde belirtilen İdareyi memnun edecek hükümleri açıklığa kavuşturmaktır. Kaldırma donanımlarının ve çapa taşıma vinçlerinin Paya takıldığından emin olmanın yanı sıra...</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-408-Lifiting-appliances-Anchor-handling-march-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MMC-195-09-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MMC-195</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MMC-195</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>The purpose of this Merchant Marine Circular is providing a revised instructions on 
+implementing, maintenance and compliance with the requirements to the Long-Range 
+Identification and Tracking of ships (LRIT) on board the Panamanian flagged vessels, as 
+required by Regulation 19-1 of Chapter V of ...</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesinin amacı, Panama bayraklı gemilerdeki gemilerin Uzun Menzilli Tanımlanması ve Takibi (LRIT) gerekliliklerinin uygulanması, sürdürülmesi ve bunlara uyum konusunda, Panama bayraklı gemilerdeki Bölüm V, Kural 19-1'in gerektirdiği şekilde revize edilmiş talimatlar sağlamaktır.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-195-09-04-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MMC-235-08-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MMC-235</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MMC-235</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users of the Panamanian 
+Registry, the regulations of the Republic of Panama and the Panama Maritime 
+Authority (PMA) by means of which the provisions of the International Convention 
+on Standards of Training, Certification and Watchkeeping ...</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Panama Sicili kullanıcılarına, Panama Cumhuriyeti ve Panama Denizcilik Otoritesi'nin (PMA) düzenlemelerini, Eğitim, Sertifikasyon ve Vardiya Standartlarına İlişkin Uluslararası Sözleşmenin hükümleri aracılığıyla iletmektir.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-235-08-04-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MMC-176-6-4-26-rev.pdf</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SMC / ISM</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MMC-176</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MMC-176</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1.1 
+This Merchant Marine Circular establishes the mandatory policy for the implementation 
+of the International Safety Management (ISM) Code, in strict alignment with International 
+Maritime Organization (IMO) guidelines. It provides a standardized framework for 
+additional verifications to ensure ...</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1.1 Bu Ticari Denizcilik Genelgesi, Uluslararası Denizcilik Örgütü (IMO) yönergeleriyle tam uyum içinde, Uluslararası Güvenlik Yönetimi (ISM) Kodunun uygulanmasına yönelik zorunlu politikayı belirlemektedir. Ek doğrulamalar için standartlaştırılmış bir çerçeve sağlar ...</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-176-6-4-26-rev sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SMS (Emniyetli Yönetim Sistemi) denetimlerinde güncelliğini kontrol edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MMC-404-Pre-Arrival-Checklist-02-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MMC-404</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>MMC-404</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this Merchant Marine Circular is to provide information on the 
+measures implemented to enhance the performance of the Panamanian Merchant 
+Marine Fleet.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1.1 Bu Ticari Denizcilik Genelgesinin amacı, Panama Ticari Denizcilik Filosunun performansını artırmak için uygulanan önlemler hakkında bilgi sağlamaktır.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-404-Pre-Arrival-Checklist-02-04-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MMC-331-DGGM-25-03-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MMC-331</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MMC-331</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users of the Panamanian 
+Registry, the original forms of certificates and technical documentation for seafarers 
+approved by the Panama Maritime Authority.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users of the Panamanian  Registry, the original forms of certificates and technical documentation for seafarers  approved by the Panama Maritime Authority.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-331-DGGM-25-03-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MMC-202-12-MARCH-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MMC-202</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MMC-202</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.1. The purpose of this Merchant Marine Circular is to inform the list of P&amp;I Clubs, 
+insurance companies, and financial security providers (Insurers) accepted by this 
+Administration to issue the Insurance Certificates or Financial Securities related to 
+following Conventions: CLC’92, BCC 2001, PA...</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2.1. Bu Deniz Ticareti Genelgesinin amacı, aşağıdaki Sözleşmelere ilişkin Sigorta Sertifikaları veya Mali Menkul Kıymetler ihraç etmek üzere bu İdare tarafından kabul edilen P&amp;I Kulüpleri, sigorta şirketleri ve mali güvenlik sağlayıcılarının (Sigortacılar) listesini bilgilendirmektir: CLC'92, BCC 2001, PA...</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-202-12-MARCH-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MMC-345-MARCH-2026-CM-rev-dccm.pdf</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MMC-345</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MMC-345</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1.1. 
+The purpose of this Merchant Marine Circular is to inform that the Republic 
+of Panama submitted to the Secretary General of the International Maritime 
+Organization, the accession of the Ballast Water Management Convention 
+2004, including a declaration in accordance with the recommendation 
+...</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1.1.  Bu Ticari Denizcilik Genelgesinin amacı, Panama Cumhuriyeti'nin Uluslararası Denizcilik Örgütü Genel Sekreterine, Balast Suyu Yönetimi Sözleşmesi 2004'e katılımını, tavsiye uyarınca bir beyan da dahil olmak üzere sunduğunu bildirmektir ...</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-345-MARCH-2026-CM-rev-dccm sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MMC-215-CM-Rev.-RB-1-06-03-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MMC-215</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MMC-215</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.1. The purpose of this Marine Circular is to provide ship-owners, ship operators, 
+Masters and officers of Panama flagged vessels with guidance on the proper 
+maintenance and keeping of the current Panama official Oil Record Book, now 
+named Oil Record Book and Emissions according to MARPOL 73/78 ...</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2.1. Bu Denizcilik Genelgesinin amacı, Panama bayraklı gemilerin armatörlerine, gemi operatörlerine, kaptanlarına ve zabitlerine, MARPOL 73/78'e göre Petrol Kayıt Defteri ve Emisyonlar olarak adlandırılan mevcut Panama resmi Petrol Kayıt Defterinin uygun şekilde bakımı ve saklanması konusunda rehberlik sağlamaktır.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-215-CM-Rev.-RB-1-06-03-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MMC-169-05-03-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MMC-169</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MMC-169</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>. 
+In this circular we inform the maritime community about the (companies) Authorities in 
+Charge of Accounting recognized by Panama as well as the Activation Points (PSA) 
+(companies) recognized by Panama.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>.    Bu genelgede denizcilik camiasını, Panama tarafından tanınan Muhasebeden Sorumlu Yetkililer (şirketler) ve Panama tarafından tanınan Aktivasyon Noktaları (PSA) (şirketler) hakkında bilgilendiriyoruz.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-169-05-03-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MMC-217-STS-28-01-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ship-owners / Operators, Company Security Officers, Designates Persons</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Armatörler / Operatörler, Şirket Güvenlik Görevlileri, Belirlenen Kişiler</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>. 
+1.1. This Merchant Marine Circular is to informs all owner/operators regarding the new</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>.    1.1. Bu Ticari Denizcilik Genelgesi, tüm gemi sahiplerini/işletmecilerini yeni</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-217-STS-28-01-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MMC-324-JAN-2026-act.pdf</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MMC-324</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MMC-324</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2.1. This Merchant Marine Circular has the aim to provide an easily access to all Recognized 
+Organizations (ROs), Recognized Security Organizations (RSOs), Classification Societies 
+duly authorized to act on behalf the Republic of Panama, to all Stakeholders of the Registry, 
+to the regulations reg...</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2.1. Bu Ticari Denizcilik Genelgesi, Panama Cumhuriyeti adına hareket etmek üzere usulüne uygun olarak yetkilendirilmiş tüm Tanınmış Kuruluşlara (RO'lar), Tanınmış Güvenlik Kuruluşlarına (RSO'lar), Sınıflandırma Kuruluşlarına, Sicil Kurumunun tüm Paydaşlarına, ilgili düzenlemelere kolayca erişim sağlamayı amaçlamaktadır.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-324-JAN-2026-act sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MMC-136-RO-20-01-2026-1.pdf</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS, Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MMC-136</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MMC-136</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>The purpose of this circular is to inform all our stakeholders about the Recognized Organizations 
+(RO) and Recognized Security Organizations (RSO) authorized to perform Statutory Certification 
+and Services on behalf of the Republic of Panama for ships registered under Panama flag. 
+3. SCOPE 
+3...</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bu genelgenin amacı, Panama bayrağı altında kayıtlı gemiler için Panama Cumhuriyeti adına Yasal Sertifikasyon ve Hizmet vermeye yetkili Tanınmış Kuruluşlar (RO) ve Tanınmış Güvenlik Kuruluşları (RSO) hakkında tüm paydaşlarımızı bilgilendirmektir.    3. KAPSAM 3...</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-136-RO-20-01-2026-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MMC-369-Modif-Ene-2026-rev-dccm.pdf</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MMC-369</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MMC-369</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1.1. Further to the information stated in the Merchant Marine Circular MMC-365, the 
+purpose of this Merchant Marine Circular is to inform the list of Authorized service 
+providers by the Panama Maritime Authority for confirmation, verification and 
+collection for the fuel oil consumption data and C...</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1.1. Ticari Denizcilik Genelgesi MMC-365'te belirtilen bilgilere ek olarak, bu Ticari Denizcilik Genelgesinin amacı, Panama Denizcilik Otoritesi tarafından akaryakıt tüketim verilerinin onaylanması, doğrulanması ve toplanması için Yetkili hizmet sağlayıcıların listesini bilgilendirmek ve...</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-369-Modif-Ene-2026-rev-dccm sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MMC-365-Modif-Ene-2026-rev-dccm.pdf</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MMC-365</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MMC-365</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Merchant Marine Circular is to inform that the Republic of 
+Panama has adopted the Resolution MEPC.328(76) dated on June 17, 2021 through 
+which the IMO has adopted the amendments to Annex VI of MARPOL 73/78. 
+1.2. Furthermore, to provide guidance and instructions to ensur...</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesinin amacı, Panama Cumhuriyeti'nin, IMO'nun MARPOL 73/78 Ek VI'daki değişiklikleri kabul ettiği 17 Haziran 2021 tarihli MEPC.328(76) Kararını kabul ettiğini bildirmektir.    1.2. Ayrıca, aşağıdakileri sağlamak için rehberlik ve talimatlar sağlamak...</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-365-Modif-Ene-2026-rev-dccm sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MMC-290-Jan-2026-rev-dccm.pdf</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MMC-290</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MMC-290</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1.1. Inform that the Republic of Panama submitted to the Secretariat of the International 
+Maritime Organization, the accession of the Athens Convention relating to the 
+Carriage of Passengers and their Luggage by Sea, 1974, on January 23, 2014, in 
+accordance with article 17. 
+1.2. Following the ...</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1.1. Panama Cumhuriyeti'nin, 17. madde uyarınca 23 Ocak 2014 tarihinde Yolcuların ve Bagajlarının Deniz Yoluyla Taşınmasına İlişkin Atina Sözleşmesi'nin (1974) katılımını Uluslararası Denizcilik Örgütü Sekretaryası'na sunduğunu bildirin. 1.2. ...</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-290-Jan-2026-rev-dccm sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MMC-269-Jan-2026-rev-dccm.pdf</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MMC-269</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MMC-269</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.1. 
+Is to inform users of the Panamanian Registry that Segumar International 
+Offices are able to issue the Declaration of Maritime Labour Compliance Part I, 
+(DMLC-Part I) in electronic format free of charge.  Within this Part (DMLC-Part 
+I) compile all national regulations required to certify th...</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2.1.  Panama Sicili kullanıcılarına, Segumar Uluslararası Ofislerinin Denizcilik İşgücü Uyumluluğu Bildirgesi Bölüm I, (DMLC-Bölüm I)'i ücretsiz olarak elektronik formatta yayınlayabileceği konusunda bilgi vermektir.  Bu Bölümde (DMLC-Bölüm I), aşağıdakileri belgelendirmek için gereken tüm ulusal düzenlemeleri derleyin:</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-269-Jan-2026-rev-dccm sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MMC-317-2026-Rev-dccm.pdf</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MMC-317</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MMC-317</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to inform all users of the Panamanian Registry that 
+the Nairobi International Convention on the Removal of Wrecks, 2007 has been 
+adopted by the Republic of Panama on February 26, 2015, and the accession has 
+been deposited at IMO on August 18, 2015.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı Panama Sicili'nin tüm kullanıcılarına, Enkazların Kaldırılmasına İlişkin Nairobi Uluslararası Sözleşmesi 2007'nin Panama Cumhuriyeti tarafından 26 Şubat 2015 tarihinde kabul edildiği ve katılımın 18 Ağustos 2015 tarihinde IMO'ya sunulduğu konusunda bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-317-2026-Rev-dccm sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MMC-194-January-2026-CM-Rev-dccm.pdf</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MMC-194</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MMC-194</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>The purpose of this circular is to inform stakeholders that this Administration has 
+established certain requirements to allow extended service intervals not exceeding 30 
+months for novel inflatable Liferafts. Hence, a uniform and equivalent level of safety is 
+maintained on board Panamanian-flagge...</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Bu genelgenin amacı, paydaşlara, bu İdarenin yeni şişirilebilir Can salları için 30 ayı aşmayacak şekilde uzatılmış servis aralıklarına izin vermek üzere belirli gereklilikler oluşturduğunu bildirmektir. Böylece Panama bandıralı gemide tek tip ve eşdeğer bir güvenlik seviyesi sağlanıyor...</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-194-January-2026-CM-Rev-dccm sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MMC-406-Rev.-DGGM-26-12-2025-rev-dccm.pdf</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MMC-406</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MMC-406</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users of the Panamanian 
+Registry, the transitional provisions of the Panama Maritime Authority (PMA) 
+regarding the new Amendments to the STCW Code on prevention and response to 
+violence and harassment, including bullying, sexual harassmen...</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Panama Sicili kullanıcılarına, Panama Denizcilik Otoritesi'nin (PMA), zorbalık, cinsel taciz de dahil olmak üzere şiddet ve tacizin önlenmesi ve bunlara tepki verilmesine ilişkin STCW Kodunda yapılan yeni Değişikliklere ilişkin geçici hükümlerini iletmektir.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-406-Rev.-DGGM-26-12-2025-rev-dccm sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MMC-281-OCTOBER-2025-CM.pdf</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MMC-281</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MMC-281</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.1. 
+Provide the minimum recommended level of maintenance and inspections for the 
+protection system and appliances. It should be noted that the general requirements 
+contained in this Circular are not an all-inclusive list of maintenance or inspection 
+items for fire protection systems, fire-fight...</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2.1.  Koruma sistemi ve cihazları için önerilen minimum bakım ve denetim seviyesini sağlayın. Bu Genelgede yer alan genel gerekliliklerin, yangından korunma sistemleri, yangınla mücadele...</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-281-OCTOBER-2025-CM sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MMC-224-Sept-2025-Rev-MR.pdf</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MMC-224</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MMC-224</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>The purpose of this circular is to inform and ensure that Panamanian-flagged ships 
+monitor the control of the quality of fuel delivered on board ships by the bunker suppliers in 
+accordance with Regulation 18 of Annex VI of the MARPOL Convention.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Bu genelgenin amacı, Panama bandıralı gemilerin, MARPOL Sözleşmesi Ek VI, Kural 18 uyarınca yakıt tedarikçileri tarafından gemilere teslim edilen yakıtın kalite kontrolünü bilgilendirmek ve izlemesini sağlamaktır.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-224-Sept-2025-Rev-MR sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MMC-405-FRA-PMAP-03-09-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MMC-405</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MMC-405</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to inform the revised measures aimed to optimize 
+the performance of the Panamanian Merchant Fleet.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Panama Ticaret Filosunun performansını optimize etmeyi amaçlayan revize edilmiş önlemler hakkında bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-405-FRA-PMAP-03-09-2025 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MMC-339-Rv-MR-Aug-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MMC- 339</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MMC- 339</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>and should be equipped with a lock. 
+8. An expiry date for a medicine corresponds to the average maximum shelf life for 
+that medicine, given appropriate storage conditions. Medicines must be inspected 
+regularly to make sure they have not reached or exceeded their expiry dates: those 
+that have sho...</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ve bir kilitle donatılmalıdır.  8. Bir ilacın son kullanma tarihi, uygun saklama koşulları göz önüne alındığında, o ilacın ortalama maksimum raf ömrüne karşılık gelir. İlaçların son kullanma tarihlerine ulaşmadığından veya geçmediğinden emin olmak için düzenli olarak kontrol edilmesi gerekir:...</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-339-Rv-MR-Aug-2025 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MMC-271-DGGM-17-07-2025-1.pdf</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MMC-271</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MMC-271</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.1. The purpose of this Circular is to communicate to the users of Panamanian 
+Registry, the regulations of the Republic of Panama and the Panama Maritime 
+Authority (PMA) by means of which the provisions of the Maritime Labour 
+Convention 2006, as amended (MLC, 2006, as amended), including 2014, 2...</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2.1. Bu Genelgenin amacı, Panama Sicili kullanıcılarına, Panama Cumhuriyeti ve Panama Denizcilik Otoritesi'nin (PMA) düzenlemelerini, 2014 dahil olmak üzere tadil edilmiş şekliyle 2006 Denizcilik Çalışma Sözleşmesi (MLC, tadil edilmiş şekliyle 2006), 2...</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-271-DGGM-17-07-2025-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MMC-359-18-08-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MMC-359</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MMC-359</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>The purpose of this Merchant Marine Circular is providing information and guidance to 
+concerning the Administrations requirements for compliance with the International Ship 
+&amp; Port Facility Security Code (ISPS Code). It also contains the Administration’s policies 
+and interpretations regarding appl...</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bu Deniz Ticareti Genelgesinin amacı, İdarenin Uluslararası Gemi ve Liman Tesisi Güvenlik Koduna (ISPS Kodu) uyum gereklilikleri konusunda bilgi ve rehberlik sağlamaktır. Ayrıca İdarenin uygulamalara ilişkin politika ve yorumlarını da içermektedir.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-359-18-08-2025 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MMC-133-14-08-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS, Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MMC-133</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MMC-133</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>The purpose of this Circular is to communicate the instructions and procedures of the Ship 
+Security Alert System (SSAS) according to SOLAS 74’, as amended Chapter XI-2 Reg. 6, 
+the IMO Resolution MSC.136(76) and Resolution No. 106-107-DGMM dated October 9th, 
+2017 (Visit: https://panamashipregistry...</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, değiştirilen Bölüm XI-2 Reg. 6, 9 Ekim 2017 tarihli IMO Kararı MSC.136(76) ve Karar No. 106-107-DGMM (Ziyaret: https://panamashipregistry...</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-133-14-08-2025 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MMC-346-13-08-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SMC / ISM, ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MMC-346</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MMC-346</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>The purpose of this Merchant Marine Circular is to inform all owners and operator 
+companies that during the process of the last RO Code Audit, this Administration 
+cancelled some Recognized Security Organizations (RSO’s) responsible for the review 
+and approval of the Ship Security Plan (SSP) for v...</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesinin amacı, tüm armatörlere ve operatör şirketlere, son RO Kodu Denetimi sürecinde, bu İdarenin, Gemi Güvenlik Planının (SSP) gözden geçirilmesinden ve onaylanmasından sorumlu bazı Tanınmış Güvenlik Organizasyonlarını (RSO'lar) iptal ettiği konusunda bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-346-13-08-2025 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SMS (Emniyetli Yönetim Sistemi) denetimlerinde güncelliğini kontrol edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MMC-123-13-8-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MMC-123</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MMC-123</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.1 The purpose of this Merchant Marine Circular was issued to provide information and 
+guidance to Ship-owner, Operators, and Master concerning the Administration’s</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2.1 Bu Deniz Ticareti Genelgesinin amacı, Gemi Sahibine, İşletmecilere ve Kaptanlara, İdarenin</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-123-13-8-2025 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MMC-243-13-08-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MMC-243</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MMC-243</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2.1 The purpose of this circular is to establish the requirements for the accreditation of 
+Private Security Companies on board Panamanian flagged vessels, as well as the 
+documents that must be presented to maintain their accreditation.  
+3. Scope: 
+3.1 This Merchant Marine Circular applies to ...</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2.1 Bu genelgenin amacı, Panama bandıralı gemilerde bulunan Özel Güvenlik Şirketlerinin akreditasyonuna ilişkin gereklilikleri ve akreditasyonlarının devamı için ibraz edilmesi gereken belgeleri belirlemektir.     3. Kapsam: 3.1 Bu Deniz Ticareti Genelgesi aşağıdakiler için geçerlidir:</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-243-13-08-2025 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MMC-386-Aug-2025-Rv-MR.pdf</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MMC-386</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MMC-386</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Merchant Marine Circular is to inform on the implementation of 
+the Hong Kong International Convention for the Safe and Environmentally Sound 
+Recycling of Ships, 2009, which enters into force on 26 June 2025. In addition, to 
+ensure that Panamanian-flagged ships comply with...</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesinin amacı, 26 Haziran 2025 tarihinde yürürlüğe girecek olan Gemilerin Güvenli ve Çevreye Duyarlı Geri Dönüşümüne İlişkin Hong Kong Uluslararası Sözleşmesinin (2009) uygulanması hakkında bilgi vermektir. Ayrıca, Panama bayraklı gemilerin...</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-386-Aug-2025-Rv-MR sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MMC-360-18-07-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS, MLC</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MMC-360</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MMC-360</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>The purpose of this Circular is to warn ship owners and operators, captains, and crew 
+members that North Korea is actively evading the sanction measures imposed by the 
+United Nations Security Council (UNSC) using a variety of deceptive practices.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, gemi sahiplerini ve operatörlerini, kaptanları ve mürettebatı, Kuzey Kore'nin çeşitli aldatıcı uygulamalar kullanarak Birleşmiş Milletler Güvenlik Konseyi (BMGK) tarafından uygulanan yaptırım önlemlerinden aktif olarak kaçındığı konusunda uyarmaktır.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-360-18-07-2025 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MMC-151-Rev.-RB-04-07-25-Rev.-RJ-7-7-25-Final-DCCM.pdf</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MMC-151</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MMC-151</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1.1. 
+The purpose of this MMC is to inform all interested parties on the use of the IMO 
+Ship Identification Number Scheme and the permanent identification number to 
+companies and registered owners, to enhance maritime safety and pollution 
+prevention and also to facilitate the prevention of mariti...</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1.1.  Bu MMC'nin amacı, denizcilik güvenliğini ve kirliliğin önlenmesini geliştirmek ve aynı zamanda deniz kirliliğinin önlenmesini kolaylaştırmak için IMO Gemi Kimlik Numarası Programının ve şirketlere ve kayıtlı gemi sahiplerine kalıcı kimlik numarasının kullanımı konusunda tüm ilgili tarafları bilgilendirmektir.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-151-Rev.-RB-04-07-25-Rev.-RJ-7-7-25-Final-DCCM sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MMC-355-MAY-2025-rev-dccm.pdf</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MMC-355</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MMC-355</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1.1. This Merchant Marine Supersedes MMC-347. 
+1.2. The purpose of this Merchant Marine Circular is to inform that the Republic of 
+Panama has welcomed the use of the Guidelines for the use of electronic 
+certificates, adopted by the International Maritime Organization by the Facilitation 
+Committ...</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1.1. Bu Merchant Marine, MMC-347'nin yerini alır.    1.2. Bu Ticari Denizcilik Genelgesinin amacı, Panama Cumhuriyeti'nin, Uluslararası Denizcilik Örgütü tarafından Kolaylaştırma Komitesi tarafından kabul edilen elektronik sertifikaların kullanımına ilişkin Kılavuzların kullanımını memnuniyetle karşıladığını bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-355-MAY-2025-rev-dccm sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MMC-403-17-04-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MMC-403</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>MMC-403</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to provide shipowners and operating companies with 
+basic recommendations to minimize the abuse of alcohol, drugs, and other 
+potentially harmful substances, and prevent the risk and concerns relating to 
+HIV/AIDS and other health risk-related activities on board...</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, armatörlere ve işletmeci şirketlere, alkol, uyuşturucu ve diğer zararlı maddelerin kötüye kullanımını en aza indirmek ve gemide HIV/AIDS ve diğer sağlık riskleriyle ilgili faaliyetlerle ilgili risk ve endişeleri önlemek için temel öneriler sunmaktır...</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-403-17-04-2025 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MMC-395-IGF-CODE-March-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MMC-395</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>MMC-395</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>. 
+1.1. The purpose of this Merchant Marine Circular is to inform Owners/Operators, 
+Recognized Organizations, Masters, and Annual Safety Inspectors on the 
+applicable procedures regarding the IGF Code and its amendments. The 
+International Code of safety for ships using gases or other low-flashpo...</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>.    1.1. Bu Ticari Denizcilik Genelgesinin amacı, Gemi Sahiplerini/İşletmecileri, Tanınmış Kuruluşları, Kaptanları ve Yıllık Güvenlik Denetçilerini, IGF Kodu ve değişikliklerine ilişkin geçerli prosedürler konusunda bilgilendirmektir. Gazlar veya diğer düşük parlama noktaları kullanan gemiler için Uluslararası Güvenlik Kodu...</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-395-IGF-CODE-March-2025 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MMC-344-Jan-2025-MR.pdf</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MMC-344</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MMC-344</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users of Panamanian 
+Registry, the restrictive measures of the Panama Maritime Authority  (PMA) 
+with respect to the recognition of seafarers' technical documentation issued by 
+other Maritime Administrations of States Parties to the 1978 ST...</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Panama Sicili kullanıcılarına, Panama Denizcilik Otoritesi'nin (PMA), 1978 ST'ye Taraf Devletlerin diğer Denizcilik İdareleri tarafından denizcilere ait teknik belgelerin tanınmasına ilişkin kısıtlayıcı tedbirlerini bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-344-Jan-2025-MR sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MMC-343-Rv-MR-JAN2025.pdf</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MMC-343</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MMC-343</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users to the Panamanian 
+Registry, the List of States Parties of the 1978 STCW Convention, as amended, to 
+which the Panama Maritime Authority recognizes the Certificates of Competency 
+(CoC) and Certificates of Proficiency (CoP), in complia...</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, kullanıcılara Panama Denizcilik Otoritesi'nin Yeterlilik Sertifikalarını (CoC) ve Yeterlilik Sertifikalarını (CoP) uygun olarak tanıdığı 1978 STCW Sözleşmesi Taraf Devletler Listesi olan Panama Siciline iletmektir.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-343-Rv-MR-JAN2025 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MMC-274-Dec-2024.pdf</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MMC-274</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MMC-274</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this Circular is to inform users of the Panamanian Registry that 
+according to the Standard A4.3.5 of the Maritime Labour Convention, 2006, as 
+amended, regarding Health and safety protection and accident prevention, the 
+occupational accidents and injuries on board must be report...</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1.1 Bu Genelgenin amacı, Panama Sicili kullanıcılarına, Sağlık ve güvenliğin korunması ve kazaların önlenmesine ilişkin değiştirilmiş şekliyle 2006 Denizcilik Çalışma Sözleşmesinin A4.3.5 Standardına göre, gemideki iş kazaları ve yaralanmaların rapor edilmesi gerektiği konusunda bilgi vermektir...</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-274-Dec-2024 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MMC-367-22-10-2024-1.pdf</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MMC-367</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MMC-367</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this Circular is to inform that this Administration has decided to provide 
+guidance to the shipowners or operator to the Panamanian flag vessels, in order to 
+avoid jobs where the crew members are exposed to hazard situations contrary to 
+safety, health and hygiene on board.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1.1 Bu Genelgenin amacı, bu İdarenin, mürettebatın gemide güvenlik, sağlık ve hijyen açısından aykırı durumlara maruz kaldığı işlerden kaçınmak amacıyla, Panama bandıralı gemilerin armatörlerine veya işletmecilerine rehberlik sağlamaya karar verdiğini bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-367-22-10-2024-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MMC-161-September-2024.pdf</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MMC-161</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>MMC-161</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Merchant Marine Circular is to communicate all parties concerned 
+with Panamanian flag ships, of the approved guidelines adopted with the purpose of 
+having a standard method for the annual testing of the VDR and S-VDR including the 
+last amendments adopted by IMO through MS...</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesinin amacı, Panama bandıralı gemilerle ilgili tüm taraflara, IMO tarafından MS aracılığıyla kabul edilen son değişiklikler de dahil olmak üzere, VDR ve S-VDR'nin yıllık testi için standart bir yönteme sahip olmak amacıyla kabul edilen onaylanmış kılavuzları iletmektir.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-161-September-2024 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MMC-350-17-10-2023-1.pdf</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MMC-350</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MMC-350</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users of the Panamanian 
+Registry, the provisions for conditions to be provided by the ship-owner to cadets 
+on board of Panamanian flag vessels.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Panama bandıralı gemilerde gemi sahibi tarafından adaylara sağlanacak şartlara ilişkin hükümleri Panama Sicili kullanıcılarına iletmektir.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-350-17-10-2023-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MMC-379-Procedure-for-PSC-24-07-2024.pdf</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MMC-379</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>MMC-379</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1.1 This Merchant Marine Circular informs that the IMO  Resolution A.1185(33) was 
+adopted on December 6, 2023, updating the Procedures for Port State Control 
+Inspections, providing basic guidance on the conduct of port State control inspections 
+in support of the control provisions of relevant con...</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1.1 Bu Ticari Denizcilik Genelgesi, Liman Devleti Kontrol Denetimleri Prosedürlerini güncelleyen ve ilgili kuralların kontrol hükümlerini desteklemek üzere liman Devleti kontrol denetimlerinin yürütülmesine ilişkin temel rehberlik sağlayan IMO Kararı A.1185(33)'ün 6 Aralık 2023'te kabul edildiğini bildirir.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-379-Procedure-for-PSC-24-07-2024 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MMC-171-08-05-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MMC-171</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>MMC-171</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Merchant Marine Circular is to inform all relevant parties of 
+the risk-based approach of the Flag Safety Inspection. 
+1.2. Based on Article 117 of Law No. 57 of 2008, the General Directorate of 
+Merchant Marine (DGMM) has updated the Flag Safety Inspection program to 
+imp...</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1.1. Bu Deniz Ticaret Genelgesinin amacı, Bayrak Emniyet Denetiminin risk bazlı yaklaşımı konusunda ilgili tüm tarafları bilgilendirmektir.    1.2. Deniz Ticareti Genel Müdürlüğü (GİGM), 2008 tarihli 57 sayılı Kanunun 117'nci maddesi uyarınca Bayrak Emniyet Denetimi programını güncelleyerek...</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-171-08-05-2026 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MMC-401-SOLAS-chapter-XV-and-IP-code.pdf</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MMC-401</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>MMC-401</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1.1. 
+This merchant marine circular provides a summary of the principal aspects of 
+the Amendments to SOLAS, new Chapter XV – Safety measures for ships 
+carrying industrial personnel, and the mandatory provisions of the International 
+Code of Safety for Ships Carrying Industrial Personnel (IP Code) ...</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1.1.  Bu ticari denizcilik genelgesi, SOLAS'taki Değişikliklerin ana yönlerinin bir özetini, yeni Bölüm XV – Endüstriyel personel taşıyan gemiler için güvenlik önlemlerini ve Endüstriyel Personel Taşıyan Gemiler için Uluslararası Güvenlik Kodunun (IP Kodu) zorunlu hükümlerinin bir özetini sunmaktadır.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-401-SOLAS-chapter-XV-and-IP-code sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MMC-288-SPS-CODE-7-JUNE-2024-rev.pdf</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MMC-288</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>MMC-288</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ships, 2008, as amended. 
+Reference:  a) Resolution MSC.266 (84) as amended, adopted by Resolution No. 106- 
+OMI-126-DGMM. 
+b) Resolution A.534 (13) as amended, adopted by Resolution No. 106- OMI-
+148-DGMM. 
+c) Resolution MSC.453 (100) of 7 December 2018 and Resolution 
+MSC.464(101) of 14 Ju...</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Gemiler, 2008, değiştirildiği şekliyle.      Referans: a) 106- OMI-126-DGMM sayılı Kararla kabul edilen, tadil edilmiş haliyle MSC.266 (84) Kararı.    b) 106- OMI- 148-GİGM Karar No. ile kabul edilen, tadil edilmiş şekliyle A.534 (13) sayılı Karar.    c) 7 Aralık 2018 tarihli Karar MSC.453 (100) ve 14 Haziran 2018 tarihli Karar MSC.464(101)...</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-288-SPS-CODE-7-JUNE-2024-rev sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MMC-391-Multiple-Load-Line-Procedure-Rev-may-2024.pdf</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MMC-391</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>MMC-391</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2.1 The purpose of this Merchant Marine Circular is to provide the operational 
+procedure to be followed to change Load Line Certificates on Panamanian 
+registered vessels when Multiple Load Line Assignment.  
+3. 
+Background 
+3.1 Multiple Load Line Certificates are used when, for a period of tim...</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2.1 Bu Ticari Denizcilik Genelgesinin amacı, Çoklu Yükleme Hattı Tahsisi durumunda Panama'ya kayıtlı gemilerdeki Yükleme Sınırı Sertifikalarını değiştirmek için izlenecek operasyonel prosedürü sağlamaktır.     3. Arka Plan 3.1 Çoklu Yükleme Hattı Sertifikaları belirli bir süre için kullanıldığında...</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-391-Multiple-Load-Line-Procedure-Rev-may-2024 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MMC-152-May-2024-REV-SEGUMAR-JGC-correccion-menor-2021-por-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MMC-152</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>MMC-152</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1.1. 
+This Merchant Marine Circular provides a summary of the principal aspects of the 
+guidelines for the implementation of the Harmonized System of Survey and 
+Certification (HSSC), 2023 on vessels flying Panama flag, aiming to serve of a 
+brief orientation for all interested parties.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1.1.  Bu Ticari Denizcilik Genelgesi, tüm ilgili taraflara kısa bir oryantasyon hizmeti sunmayı amaçlayan, 2023 Harmonize Sörvey ve Sertifikasyon Sisteminin (HSSC) Panama bandıralı gemilerde uygulanmasına yönelik kılavuzların temel yönlerinin bir özetini sunmaktadır.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-152-May-2024-REV-SEGUMAR-JGC-correccion-menor-2021-por-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MMC-204-Rev-RB-JGC-April-2024.pdf</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MMC-204</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>MMC-204</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2.1 This Circular has the purpose to clarify on the inspection of the outside of the ship's 
+bottom. The instructions described in this circular have been prepared considering the 
+Survey Guidelines under the Harmonized System of Survey and Certification, 2023 set 
+out in the annex of the Resolution...</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2.1 Bu Genelge, gemi karinasının dış muayenesine açıklık getirmeyi amaçlamaktadır. Bu genelgede açıklanan talimatlar Karar ekinde yer alan 2023 Harmonize Sörvey ve Belgelendirme Sistemi Kapsamındaki Sörvey Kılavuzları dikkate alınarak hazırlanmıştır...</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-204-Rev-RB-JGC-April-2024 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MMC-156-April-2024-Rev.pdf</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MMC-156</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>MMC-156</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2.1. 
+The purpose of this Merchant Marine Circular is to clarify the policy of this 
+Administration in connection to the issuance of Exemption, Equivalents Conditional, 
+Interim and Full-Term Certificates. 
+3. Scope 
+3.1. 
+This Circular provides definitions for various types of certificates issu...</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2.1.  Bu Deniz Ticareti Genelgesinin amacı, bu İdarenin Muafiyet, Eşdeğer Şartlı, Geçici ve Tam Süreli Sertifikaların düzenlenmesine ilişkin politikasını açıklığa kavuşturmaktır.    3. Kapsam 3.1.  Bu Genelge, düzenlenen çeşitli sertifika türlerine ilişkin tanımlar sağlar...</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-156-April-2024-Rev sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MMC-138-02-04-2024-2.pdf</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MMC-138</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>MMC-138</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1.1. 
+The purpose of this Merchant Marine Circular is to establish guidelines for 
+maintaining and testing magnetic compasses.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1.1.  Bu Ticari Denizcilik Genelgesinin amacı, manyetik pusulaların bakımı ve test edilmesine ilişkin yönergeler oluşturmaktır.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-138-02-04-2024-2 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MMC-150-13-03-2024.pdf</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MMC-150</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>MMC-150</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1.1 This merchant marine circular establishes an Alternative Program to carry out flag 
+State Inspections (FSIs) on board any type of Mobile Offshore Units (MOU) under 
+the flag of Panama, regardless of its on-location for drilling, accommodation, 
+production and/or storage or any other operation of...</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1.1 Bu ticari denizcilik genelgesi, sondaj, konaklama, üretim ve/veya depolama veya diğer herhangi bir operasyon için bulunduğu yere bakılmaksızın, Panama bayrağı altındaki her türlü Mobil Açık Deniz Biriminde (MOU) bayrak Devleti Denetimlerini (FSI'ler) yürütmek için bir Alternatif Program oluşturur.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-150-13-03-2024 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MMC-192-TYPE-APPROVAL-ADMINISTRATION-CRITERIA-REV-March-2024.pdf</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MMC-192</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>MMC-192</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1.1. 
+The purpose of this Circular is to issue guidance on “Type approvals” and “the 
+satisfaction of the Administration” criteria, in accordance with Resolution 
+No.106-002 of January 4, 2024 which revokes Resolution No. 106-181-DGMM 
+of  December 24, 2021, this Resolution revokes previous Resoluti...</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1.1.  Bu Genelgenin amacı, 24 Aralık 2021 tarih ve 106-181-GİGM Kararı'nı yürürlükten kaldıran 4 Ocak 2024 tarih ve 106-002 sayılı Karar uyarınca "Tip onayları" ve "İdarenin memnuniyeti" kriterlerine ilişkin rehberlik yapmaktır.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-192-TYPE-APPROVAL-ADMINISTRATION-CRITERIA-REV-March-2024 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MMC-376-06-03-2024.pdf</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MMC-376</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>MMC-376</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this Merchant Marine Circular is to advise Ship owners/ operators 
+and masters on the Phase out and prohibition on installation of equipment containing 
+ozone depleting Substances (ODS), including hydrochlorofluorocarbons (HCFCs).</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1.1 Bu Ticari Denizcilik Genelgesinin amacı, Gemi sahiplerine/operatörlerine ve kaptanlara, hidrokloroflorokarbonlar (HCFC'ler) dahil olmak üzere ozon tabakasını incelten Maddeler (ODS) içeren ekipmanların kurulumunun aşamalı olarak durdurulması ve yasaklanması konusunda tavsiyelerde bulunmaktır.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-376-06-03-2024 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MMC-334-GMDSS-REQUIREMENTS-March-2024-1.pdf</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MMC-334</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>MMC-334</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2.1.  The Purpose of this Circular is to remind 
+interested parties of the 
+radiocommunication performance and functionality due to the Global Maritime 
+Distress and Safety System (GMDSS) modernization. 
+ F-33 
+  (DCCM) 
+  V.04 
+3. Applicability / Scope 
+3.1. All vessels to which Radio equ...</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2.1.  Bu Genelgenin Amacı, Küresel Deniz Tehlike ve Güvenlik Sistemi (GMDSS) modernizasyonu nedeniyle ilgili taraflara telsiz haberleşme performansı ve işlevselliğini hatırlatmaktır.   F-33 ​​(DCCM) V.04 3. Uygulanabilirlik / Kapsam 3.1. Radyonun uyumlu olduğu tüm gemiler...</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-334-GMDSS-REQUIREMENTS-March-2024-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MMC-388-January-2024.pdf</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SMC / ISM</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>MMC-388</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>MMC-388</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1.1. 
+This merchant marine circular provides a summary of the principal aspects of 
+the Revised Guidelines on the Implementation of the ISM Code by 
+Administrations (Resolution A.1118(30), as applicable for companies and 
+vessels flying Panama flag, aiming to serve of a brief orientation for all 
+in...</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1.1.  Bu deniz ticaret genelgesi, ISM Kodunun İdareler Tarafından Uygulanmasına İlişkin Gözden Geçirilmiş Kılavuz'un (Karar A.1118(30) Panama bayrağı taşıyan şirketler ve gemiler için geçerli olan) temel yönlerinin bir özetini sunmakta olup, herkes için kısa bir oryantasyon hizmeti sunmayı amaçlamaktadır.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-388-January-2024 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SMS (Emniyetli Yönetim Sistemi) denetimlerinde güncelliğini kontrol edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MMC-362-January-2024-Rev.pdf</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MMC-362</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>MMC-362</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>of this Merchant Marine Circular is to inform the list of Companies with 
+Type Approval Certificate of Ballast Water Management System, accepted by this 
+Administration following the requirements and specifications according to the 
+Guidelines contained in IMO resolution MEPC.174 (58) or MEPC.279 (7...</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Bu Deniz Ticaret Genelgesi'nin amacı, IMO karar MEPC.174 (58) veya MEPC.279 (7...</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-362-January-2024-Rev sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MMC-214-IMPLEMENTATION-OF-THE-IMSBC-CODE-AMENDM-REV-DEC-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MMC-214</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>MMC-214</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1.1.  The purpose of this Merchant Marine Circular is to inform about the International 
+Maritime Solid Bulk Cargoes (IMSBC) adopted by IMO Res.MSC.268 (85) which 
+will be effective from 01 January 2011. 
+1.2. Amendments to the International Maritime Solid Bulk Cargoes (IMSBC) adopted 
+by IMO Reso...</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1.1.  Bu Deniz Ticareti Genelgesinin amacı, IMO Res.MSC.268 (85) tarafından kabul edilen ve 01 Ocak 2011 tarihinden itibaren geçerli olacak Uluslararası Denizyolu Katı Dökme Yükleri (IMSBC) hakkında bilgi vermektir. 1.2. IMO Kararı tarafından kabul edilen Uluslararası Denizcilik Katı Dökme Yüklerine (IMSBC) ilişkin değişiklikler</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-214-IMPLEMENTATION-OF-THE-IMSBC-CODE-AMENDM-REV-DEC-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MMC-366-MARPOL-Annex-V-rev-dec-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MMC-366</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MMC-366</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this Merchant Marine Circular is to provide Panamanian flagged 
+ships with general guidelines for the implementation of the Revised Annex V 
+(Regulations for the Prevention of Pollution by Garbage from Ships) of the 
+“International Convention for the Prevention of pollution from S...</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1.1 Bu Ticari Denizcilik Genelgesinin amacı, Panama bandıralı gemilere, "Güney Denizlerden Kaynaklanan Kirliliğin Önlenmesine İlişkin Uluslararası Sözleşme"nin Revize Edilmiş Ek V'inin (Gemilerden Kaynaklanan Çöpler Yoluyla Kirliliğin Önlenmesine İlişkin Yönetmelik) uygulanmasına ilişkin genel yönergeler sağlamaktır.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-366-MARPOL-Annex-V-rev-dec-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MMC-385-Dec-2023-MR.pdf</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MLC, Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MMC-385</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>MMC-385</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to inform to the users of the Panamanian 
+Registry, that based on Regulation 3.2, Standard A3.2, paragraph 6 of the 
+Maritime Labour Convention, 2006, as amended (MLC, 2006, as amended), 
+the Panama Maritime Authority (PMA) may issue a Dispensation for Ship´s 
+Co...</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Panama Sicili kullanıcılarına, değiştirildiği şekliyle (MLC, 2006, değiştirildiği şekliyle) 2006 Denizcilik Çalışma Sözleşmesinin 3.2, Standart A3.2, paragraf 6'sına dayanarak Panama Denizcilik Otoritesi'nin (PMA), Gemi Taşımacılığı için bir Muafiyet düzenleyebileceğini bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-385-Dec-2023-MR sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MMC-275-18-15-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MMC-275</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>MMC-275</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users of the Panamanian 
+Registry, the provisions applicable to food and catering in accordance with 
+Regulation 3.2, Standard A3.2 of the Maritime Labour Convention, 2006, as 
+amended (MLC, 2006, as amended).</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Panama Sicili kullanıcılarına, değiştirildiği şekliyle 2006 Denizcilik Çalışma Sözleşmesinin (MLC, 2006, değiştirildiği şekliyle) Düzenleme 3.2, Standart A3.2 Standardı uyarınca gıda ve ikram hizmetlerine uygulanabilir hükümleri iletmektir.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-275-18-15-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MMC-373-05-12-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MMC-373</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>MMC-373</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this Merchant Marine Circular is to officially communicate that on 
+August 1st, 2018, the use of the new Global Maritime Safety Inspection Platform 
+(GMSIPI) was implemented.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1.1 Bu Ticari Denizcilik Genelgesinin amacı, 1 Ağustos 2018 tarihinde yeni Küresel Deniz Güvenliği Denetim Platformu'nun (GMSIPI) kullanımının uygulamaya konulduğunu resmi olarak duyurmaktır.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-373-05-12-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MMC-03-20-11-2023-Lista-de-Consulados-1.pdf</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MMC-3</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>MMC-3</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>For knowledge the Panama Merchant Marine Consulate’s updated list authorized to receive 
+and process applications for the provisional registration of ships, preliminary recording of 
+title deeds, pre-cancellation notices and mortgages of vessels of the national merchant 
+marine.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Bilgi olarak, Panama Ticari Denizcilik Konsolosluğu'nun güncellenmiş listesi, gemilerin geçici tescili, tapu ön kayıtları, ön iptal bildirimleri ve ulusal ticari denizcilik gemilerinin ipoteklerine ilişkin başvuruları almaya ve işlemeye yetkilidir.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-03-20-11-2023-Lista-de-Consulados-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MMC-164-JMBC-08-11-2023-1.pdf</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MMC-164</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>MMC-164</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1.1. 
+The purpose of this Merchant Marine Circular is to inform recommendations of The 
+Maritime Safety Committee, of IMO for decision-making emanating from various 
+formal safety assessment (FSA) studies on bulk carrier safety. 
+1.2. 
+The Maritime Safety Committee of IMO Concluded at its MSC Circ...</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1.1.  Bu Ticari Denizcilik Genelgesinin amacı, dökme yük gemilerinin güvenliğine ilişkin çeşitli resmi güvenlik değerlendirmesi (FSA) çalışmalarından kaynaklanan karar alma süreçlerine yönelik olarak IMO'nun Deniz Güvenliği Komitesi'nin tavsiyelerine bilgi vermektir.    1.2.  IMO Deniz Emniyeti Komitesi MSC Toplantısını Tamamladı</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-164-JMBC-08-11-2023-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MMC-68-Manning-of-survival-craft-and-supervision-rev-1-D-Nov2023.pdf</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MMC-68</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MMC-68</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1.1. 
+Since the 1983 Amendments to SOLAS 74 came into force on 1 July 1986 a 
+new Chapter III is included - "Lifesaving Appliances and Arrangements". 
+Regulation 10 of this Chapter reflects new requirements for the manning of 
+survival craft.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1.1.  SOLAS 74'te yapılan 1983 Değişikliklerinin 1 Temmuz 1986'da yürürlüğe girmesinden bu yana yeni bir Bölüm III eklenmiştir - "Hayat Kurtarma Gereçleri ve Düzenlemeleri".  Bu Bölümün 10. Kuralı, can kurtarma araçlarının personel bulundurulmasına ilişkin yeni gereklilikleri yansıtmaktadır.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-68-Manning-of-survival-craft-and-supervision-rev-1-D-Nov2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MMC-328-14-11-2023-1.pdf</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MMC-328</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>MMC-328</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users of the Panamanian 
+Registry, the provisions for the training and certification of offshore personnel on 
+board offshore units registered under the Panamanian flag, in compliance with 
+the recommendations of the Resolution A.1079(28) of...</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Panama Sicili kullanıcılarına, Panama bayrağı altında kayıtlı açık deniz birimlerindeki açık deniz personelinin eğitimi ve belgelendirilmesine ilişkin hükümleri, Karar A.1079(28)'in tavsiyelerine uygun olarak iletmektir.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-328-14-11-2023-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MMC-30-COLREG-72-13-11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>MMC-30</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>MMC-30</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>. 
+1.1. The purpose of this Merchant Marine Circular is to inform Owners/Operators, 
+Recognized Organizations, Masters, and Flag State Surveyors on the applicable 
+procedures regarding the amendments to the COLREG 72. By means of Law No. 7 
+of 9 November 1978, the Republic of Panama has adopted th...</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>.    1.1. Bu Ticari Denizcilik Genelgesinin amacı, Gemi Sahiplerini/İşletmecileri, Tanınmış Kuruluşları, Kaptanları ve Bayrak Devleti Sörveyörlerini COLREG 72'de yapılan değişikliklere ilişkin uygulanabilir prosedürler konusunda bilgilendirmektir. 9 Kasım 1978 tarih ve 7 Sayılı Kanun aracılığıyla Panama Cumhuriyeti,...</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-30-COLREG-72-13-11-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MMC-167-JMBC-14-11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MLC, Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>MMC-167</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>MMC-167</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1.1. 
+The purpose of this Circular is to inform users of the Panamanian Registry that this 
+Administration has decided that based on the SOLAS Convention definitions, a 
+vessel that carries more than 12 passengers is categorized as a passenger ship. 
+Since a crew boat normally carries over 12 passen...</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1.1.  Bu Genelgenin amacı, Panama Sicili kullanıcılarına, İdarenin, SOLAS Konvansiyonu tanımlarına göre 12'den fazla yolcu taşıyan bir geminin yolcu gemisi olarak sınıflandırılmasına karar verdiği konusunda bilgi vermektir.  Bir mürettebat teknesi normalde 12 yolcu taşıdığından...</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-167-JMBC-14-11-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MMC-166-JMBC-14-11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>MMC-166</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>MMC-166</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1.1. 
+The purpose of this MMC is communicate the MSC.1/Circular.1243 requests that the 
+area where these remotely located survival craft are stowed should be provided with 
+an embarkation ladder or other means of embarkation enabling descent to the water 
+in a controlled manner in accordance with SO...</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>1.1.  Bu MMC'nin amacı, MSC.1/Circular.1243'ün, bu uzak konumdaki can kurtarma araçlarının istiflendiği alanın, SO'ya uygun olarak kontrollü bir şekilde suya inmeyi sağlayan bir binme merdiveni veya başka binme araçları ile donatılması gerektiğini talep ettiğini iletmektir.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-166-JMBC-14-11-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MMC-216-JMBC-14-11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>MMC-216</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>MMC-216</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1.1. 
+The purpose of this Merchant Marine Circular is inform to inform that the Republic of 
+Panama, through Resolution No. 106-60-DGMM of June 29, 2017 adopted the Code 
+of Safety for Caribbean Cargo Ships (CCSS Code) as amended and its revision of 
+June 3, 2015. 
+1.2. 
+The Code of Safety for Car...</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1.1.  Bu Deniz Ticareti Genelgesinin amacı, Panama Cumhuriyeti'nin 29 Haziran 2017 tarih ve 106-60-GİGM Kararı ile Karayip Kargo Gemileri için Emniyet Kurallarını (CCSS Kodu) değiştirildiği şekliyle ve 3 Haziran 2015 tarihli revizyonunu kabul ettiğini bildirmektir. 1.2.  Araç Güvenliği Kuralları...</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-216-JMBC-14-11-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MMC-241-SD-14-11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>MMC-241</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>MMC-241</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>The purpose of this Circular is to inform our users of the Registry that in order to provide the 
+most efficient as well as the highest quality service, we are pleased to provide you with the 
+new guidelines to be followed in order to obtain and/or renew the Certificate of Liability for Oil 
+Polluti...</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Sicil kullanıcılarımıza, en verimli ve en kaliteli hizmeti sunmak amacıyla, Petrol Kirliliği Sorumluluk Belgesi'nin alınması ve/veya yenilenmesi için uyulması gereken yeni yönergeleri sizlere sunmaktan memnuniyet duyduğumuzu bildirmektir...</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-241-SD-14-11-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>MMC-218-SD-14-11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MMC-218</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>MMC-218</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>The purpose of this Circular is to inform all ship-owners, operators, Recognized 
+Organizations, Master and officers of vessels registered in our Flag the entry in force of 
+Resolution 106-OMI-85-DGMM of November 22, 2010 by which this Administration adopts 
+Resolution MSC.282(86) that included, amo...</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, İdaremizin MSC.282(86) Kararını benimsediği 22 Kasım 2010 tarih ve 106-OMI-85-GİGM Kararının yürürlüğe girdiğini tüm armatörlere, operatörlere, Tanınmış Kuruluşlara, Bayrağımızda kayıtlı gemilerin kaptanlarına ve zabitlerine bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-218-SD-14-11-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>MMC-372-Nov-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MMC-372</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>MMC-372</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this Merchant Marine Circular is to provide Panamanian flagged 
+ships on the early implementation of amendment to Regulation 10 of Chapter II-2 
+of the International Convention for the Safety of Life at Sea 1974, as amended 
+(SOLAS), adopted on 25 November 2016, considering the MS...</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1.1 Bu Ticari Denizcilik Genelgesinin amacı, Panama bandıralı gemilere, MS 25 Kasım 2016'da kabul edilen, değiştirilmiş şekliyle (SOLAS) 1974 Denizde Can Güvenliği Uluslararası Sözleşmesi Bölüm II-2'nin 10. Kuralında yapılan değişikliğin erken uygulanması hakkında bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-372-Nov-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MMC-370-Nov-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MMC-370</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>MMC-370</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this Merchant Marine Circular is to inform all our clients that our 
+Administration adopted the Red Ensign Group Yacht Code (January Edition 2019) 
+through Resolution No. 106- 82-DGMM dated 12 September 2018, that has been 
+developed by United Kingdom, the Crown Dependencies and t...</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1.1 Bu Merchant Marine Genelgesinin amacı, tüm müşterilerimize, İdaremizin, Birleşik Krallık, Crown Bağımlılıkları ve t...</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-370-Nov-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MMC-378-Nov-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>MMC-378</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>MMC-378</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this Circular is to inform users of the Panama Flag Registry about   
+the content of Resolution MSC.403 (96) (Adopted on May 19, 2016), and the 
+Resolutions MSC.410(97) (Adopted on November 25, 2016), both of them 
+establishing Amendments to the International CODE for Fire Safety ...</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1.1 Bu Genelgenin amacı, Panama Bayrağı Sicili kullanıcılarını, her ikisi de Uluslararası Yangın Güvenliği KOD'unda Değişiklikler oluşturan MSC.403 (96) (19 Mayıs 2016 tarihinde kabul edilmiştir) ve MSC.410(97) (25 Kasım 2016 tarihinde kabul edilmiştir) Kararlarının içeriği hakkında bilgilendirmektir...</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-378-Nov-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MMC-259-SD-08-11-2023-1.pdf</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MMC-259</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>MMC-259</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>To inform all users of the Panamanian Registry about our policy in regards to 
+carrying on board the Annual Taxes Receipt.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Panama Sicili'nin tüm kullanıcılarını Yıllık Vergi Makbuzunun taşınmasına ilişkin politikamız hakkında bilgilendirmek.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-259-SD-08-11-2023-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MMC-229-SD-08-11-2023-1-1.pdf</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MMC-229</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>MMC-229</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Is to inform all users that the SOLAS Chapter V Regulation 19, as amended by 
+Resolution MSC.282(86), has introduced carriage requirements for BNWAS for many ships.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>MSC.282(86) Kararı ile değiştirilen SOLAS Bölüm V Düzenleme 19'un birçok gemi için BNWAS için taşıma gereklilikleri getirdiğini tüm kullanıcılara bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-229-SD-08-11-2023-1-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MMC-142-JMBC-08-11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MMC-142</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>MMC-142</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>. 
+1.1. 
+This Merchant Marine Circular replaces MMC-119.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>.    1.1.  Bu Ticari Denizcilik Genelgesi MMC-119'un yerine geçer.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-142-JMBC-08-11-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>MMC-313-Rev.-NA-02-11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MMC-313</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>MMC-313</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this circular is to inform that on board of Panamanian Flagged 
+Vessels, shall be valid for a period no longer than ninety (90) calendars day, counting 
+from the issuing date of the respective documents, full color copy of the following 
+documents, as evidence that the application...</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1.1 Bu sirkülerin amacı, Panama Bayraklı Gemilerde, ilgili belgelerin düzenlendiği tarihten itibaren doksan (90) takvim gününü geçmeyecek bir süre için geçerli olacağını, başvurunun kanıtı olarak aşağıdaki belgelerin tam renkli kopyasının geçerli olacağını bildirmektir...</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-313-Rev.-NA-02-11-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MMC-155-AIS-Oct2023.pdf</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MMC-155</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>MMC-155</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2.1. The purpose of this Merchant Marine Circular is to remind all parties concerned 
+with Panamanian flag ships of the full implementation of the carriage of AIS on 
+board Panamanian flag ships as well as the approved guidelines adopted for 
+annual testing of the Automatic Identification System. 
+ ...</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2.1. Bu Ticari Denizcilik Genelgesinin amacı, Panama bayraklı gemilerle ilgili tüm taraflara, Panama bayraklı gemilerde AIS taşıma işleminin tam olarak uygulandığını ve ayrıca Otomatik Tanımlama Sisteminin yıllık testi için kabul edilen onaylanmış yönergeleri hatırlatmaktır.   ...</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-155-AIS-Oct2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>MMC-181-16-10-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>MMC-181</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>MMC-181</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users of the Panamanian 
+Registry, the provisions of the Panama Maritime Authority (PMA) with respect to 
+the responsibilities of companies under Regulation I/14 and Section A-I/14 of the 
+1978 STCW Convention, as amended and its STCW Code.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı Panama Sicili kullanıcılarına, Panama Denizcilik Otoritesi'nin (PMA), değiştirilmiş şekliyle 1978 STCW Sözleşmesinin I/14 Yönetmeliği ve A-I/14 Bölümü kapsamında şirketlerin sorumluluklarına ilişkin hükümlerini ve STCW Kodu'nu iletmektir.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-181-16-10-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>MMC-246-Protective-Coatings-of-Dedicated-Seawater-Ballast-Tanks-in-all-Types-of-Ships-and-Double-side-Skin-Spaces-of-Bulk-Carriers-PSPC-Rev-October-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MMC-246</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>MMC-246</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1.1.   To  inform users about the position of this Administration regarding the Unified 
+Interpretation of the Application of Regulations Governed by the Building Contract 
+Date, The Keel Laying Date and the Delivery Date for the requirements of SOLAS 
+II-1/3-2 Convention (PSPC).</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1.1.   Kullanıcıları, SOLAS II-1/3-2 Konvansiyonu (PSPC) gereklilikleri için İnşaat Sözleşme Tarihi, Omurga Döşeme Tarihi ve Teslim Tarihine Göre Düzenlenen Yönetmeliklerin Uygulanmasının Birleşik Yorumuna ilişkin bu İdarenin konumu hakkında bilgilendirmek.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-246-Protective-Coatings-of-Dedicated-Seawater-Ballast-Tanks-in-all-Types-of-Ships-and-Double-side-Skin-Spaces-of-Bulk-Carriers-PSPC-Rev-October-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>MMC-87-Panama-Policy-on-MODU-Code-and-Offshore-Drilling-Units-Rev-Oct-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MMC-87</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>MMC-87</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2.1 This merchant marine circular establishes the guidelines for the application of the 
+”Code for the Construction and Equipment of Mobile Offshore Drilling Units, 1979” 
+to existing Mobile Offshore Drilling Units (MODUs) and the applicability of the IMO 
+MODU Codes 1979, 1989 and 2009 to MODUs und...</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2.1 Bu ticari denizcilik genelgesi, "Mobil Açık Deniz Sondaj Birimlerinin Yapısı ve Ekipmanı Kodu, 1979"un mevcut Mobil Açık Deniz Sondaj Birimlerine (MODU'lar) uygulanmasına ve IMO MODU Kodları 1979, 1989 ve 2009'un MODU'lara ve...</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-87-Panama-Policy-on-MODU-Code-and-Offshore-Drilling-Units-Rev-Oct-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MMC-261-16-10-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>MMC-261</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>MMC-261</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate the users of the Panamanian 
+Ship Registry that all seafarers requesting or holding a certificate or 
+endorsement issued pursuant to the provisions of the 1978 STCW Convention, 
+as amended, and providing service on board ships of Panamanian flag, m...</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı Panama Gemi Sicili kullanıcılarına, değiştirilmiş şekliyle 1978 STCW Konvansiyonu hükümleri uyarınca verilmiş bir sertifika veya onay talep eden veya bu belgeye sahip olan ve Panama bandıralı gemilerde hizmet veren tüm denizcilerin,...</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-261-16-10-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>MMC-264-13-10-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MMC-264</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>MMC-264</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users of the Panamanian 
+Registry that as per the on-board complaints procedure established in the 
+Maritime Labour Convention, 2006, as amended (MLC, 2006, as amended), all 
+Panamanian ships must keep on board the procedure for the fair, ef...</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Panama Sicili kullanıcılarına, tadil edilmiş şekliyle (MLC, 2006, tadil edilmiş şekliyle) Denizcilik Çalışma Sözleşmesi 2006'da belirlenen gemi içi şikayet prosedürü uyarınca, tüm Panama gemilerinin fuar prosedürünü yerine getirmesi gerektiğini iletmektir.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-264-13-10-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MMC-263-cancelled.pdf</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MMC-263</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>MMC-263</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>of this Circular is to provide users of the Panamanian Registry, with the 
+contact names of the persons to whom they should direct their consults in regards to 
+the implementation, application and future entry into force of the Maritime Labour 
+Convention, 2006 (MLC, 2006), amended.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına, değiştirilmiş Denizcilik Çalışma Sözleşmesi 2006'nın (MLC, 2006) uygulanması, uygulanması ve gelecekte yürürlüğe girmesiyle ilgili olarak danışmalarını yönlendirmeleri gereken kişilerin iletişim adlarını sağlamaktır.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-263-cancelled sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>MMC-203-Material-Safety-Data-Sheet-MSDS-for-ships-carrying-oil-or-oil-fuel-Rev-October-2023-REV.pdf</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MMC-203</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>MMC-203</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1.1.  The purpose of this Circular is to provide the guidelines on regards to the Material 
+Safety Data Sheet, which entered into force on 1 July 2009.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1.1.  Bu Genelgenin amacı, 1 Temmuz 2009 tarihinde yürürlüğe giren Malzeme Güvenlik Bilgi Formuna ilişkin esasları sunmaktır.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-203-Material-Safety-Data-Sheet-MSDS-for-ships-carrying-oil-or-oil-fuel-Rev-October-2023-REV sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MMC-162-cancelada.pdf</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MMC-162</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>MMC-162</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Merchant Marine Circular is to communicate all parties 
+concerned with Panamanian flag ships of the new approved fees for the issuance 
+of Exemption Certificates by Panama Maritime Authority (PMA).</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesinin amacı, Panama bandıralı gemilerle ilgili tüm taraflara, Panama Denizcilik Otoritesi (PMA) tarafından Muafiyet Sertifikalarının düzenlenmesine ilişkin yeni onaylanmış ücretleri bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-162-cancelada sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>MMC-200-MARPOL-7378-Annex-II-and-IBCBCH-Code-relative-matters-october-29-2023-rev-2-nuevo-1.pdf</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>MMC-200</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>MMC-200</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1.1. This Merchant Marine Circular supersede MMC-62, MMC-147 and MMC-186. 
+1.2. The purpose of this Merchant Marine Circular is to inform Owners/Operators, 
+Recognized Organizations, Masters, and Annual Safety Inspectors on the 
+applicable procedures related to the amendments to the IBC Code, BCH ...</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesi, MMC-62, MMC-147 ve MMC-186'nın yerine geçer.    1.2. Bu Ticari Denizcilik Genelgesinin amacı, Gemi Sahiplerini/Operatörleri, Tanınmış Kuruluşları, Kaptanları ve Yıllık Güvenlik Denetçilerini IBC Kodu, BCH ...</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-200-MARPOL-7378-Annex-II-and-IBCBCH-Code-relative-matters-october-29-2023-rev-2-nuevo-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>MMC-186-CANCELLED.pdf</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>MMC-186</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>MMC-186</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>of this Merchant Marine Circular is to remind all Panamanian flagged 
+vessels, covered by the application of Regulation 6.3, Annex II, of the International 
+Convention for the Prevention of Pollution from Ships, 1973/1978, of the mandatory 
+compliance of the requirements listed below and to inform t...</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi'nin amacı, 1973/1978 Gemilerden Kaynaklanan Kirliliğin Önlenmesine İlişkin Uluslararası Sözleşme'nin 6.3, Ek II Kuralının uygulanması kapsamındaki tüm Panama bayraklı gemilere, aşağıda listelenen gerekliliklerin zorunlu olarak yerine getirildiğini hatırlatmak ve...</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-186-CANCELLED sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>MMC-157-Oct-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>MMC-157</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>MMC-157</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Merchant Marine Circular is to officially communicate that the 
+Republic of Panama has deposited at IMO, the ratification of the International 
+Convention on the Control of Harmful Anti-Fouling System on Ships (AFS 
+Convention) in September 2007. Therefore, the Convention en...</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesinin amacı, Panama Cumhuriyeti'nin Gemilerde Zararlı Kirlenme Önleyici Sistemin Kontrolüne İlişkin Uluslararası Sözleşmenin (AFS Sözleşmesi) Eylül 2007'de onaylandığını IMO'ya tevdi ettiğini resmi olarak bildirmektir. Bu nedenle, Sözleşme...</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-157-Oct-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MMC-250-LIFEBOAT-ONLOAD-RELEASE-AND-RETRIEVAL-SYSTEM-LRRS-rev-1-oct-2023-NUEVO.pdf</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>MMC-250</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>MMC-250</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this Merchant Marine Circular is to inform all parties concerned 
+with Panamanian flag ships about MSC.1/Circ. 1392, MSC.1/Circ.1392/Corr.1 and 
+MSC.1/Circ.1584 which amendment the existing text of appendix 4 as well as the 
+amendments to Regulation III/1.5 of SOLAS and to LSA Cod...</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1.1 Bu Ticari Denizcilik Genelgesinin amacı Panama bandıralı gemilerle ilgili tüm tarafları MSC.1/Circ hakkında bilgilendirmektir. 1392, MSC.1/Circ.1392/Corr.1 ve MSC.1/Circ.1584, ek 4'ün mevcut metninin yanı sıra SOLAS Düzenleme III/1.5 ve LSA Kod'unda yapılan değişiklikleri tadil eder...</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-250-LIFEBOAT-ONLOAD-RELEASE-AND-RETRIEVAL-SYSTEM-LRRS-rev-1-oct-2023-NUEVO sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>MMC-251-Oct-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MMC- 251</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>MMC-251</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform users of the Panamanian Registry that this 
+Administration has decided that the certification required by Regulation 5.1.3 and 
+Standard A5.1.3 regarding to Maritime Labour Certificate and Declaration of Maritime 
+Labour Compliance of the Maritime Labour Convention, 200...</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına, bu İdarenin, Denizcilik Çalışma Sertifikası ve Denizcilik Çalışma Sözleşmesi Denizcilik Çalışması Uygunluk Bildirgesi, 200'e ilişkin Yönetmelik 5.1.3 ve Standart A5.1.3'ün gerektirdiği sertifikasyonun gerekli olduğuna karar verdiği konusunda bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-251-Oct-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>MMC-209-Oct-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MMC-209</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>MMC-209</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1.1.  The purpose of this circular is to inform about the resolution MEPC 176 (58), 
+which will be coming into force on 1st July 2010, which amends MARPOL Annex 
+VI regulation 15.6.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1.1.  Bu sirkülerin amacı, MARPOL Ek VI yönetmeliği 15.6'yı değiştiren, 1 Temmuz 2010 tarihinde yürürlüğe girecek olan MEPC 176 (58) sayılı karar hakkında bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-209-Oct-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>MMC-113-11-10-2023-Rev-01-RC.pdf</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>MMC-113</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>MMC-113</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>The purpose of this MMC is to inform the guidelines and criteria associated with 
+SOLAS regulation V/11 and should, in accordance with regulation V/11, be complied 
+with by Contracting Governments when planning and proposing ship reporting systems 
+to the Organization for adoption and implementing s...</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Bu MMC'nin amacı, SOLAS yönetmeliği V/11 ile ilgili yönergeleri ve kriterleri bilgilendirmek olup, yönetmelik V/11 uyarınca, Sözleşmeye Taraf Hükümetler tarafından, gemi raporlama sistemlerinin benimsenmesi ve uygulanması için Organizasyona planlanırken ve teklif edilirken bunlara uyulmalıdır.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-113-11-10-2023-Rev-01-RC sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>MMC-71-09-10-2023-1.pdf</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>MMC-71</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>MMC-71</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>The purpose of this Circular is to inform users of the following list of documents 
+required to be kept on board Panamanian flag vessels. 
+3. Scope: 
+This Merchant Marine Circular applies to Shipowners/Operators, Company Safety 
+Officers, Legal Representatives of Panama Flag Vessels, Panama Merc...</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama bandıralı gemilerde bulundurulması gereken aşağıdaki belgeler listesi hakkında kullanıcıları bilgilendirmektir.    3. Kapsam: Bu Deniz Ticareti Genelgesi, Armatörler/İşletmeciler, Şirket Güvenlik Görevlileri, Panama Bayraklı Gemilerin Yasal Temsilcileri, Panama Mercileri için geçerlidir.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-71-09-10-2023-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>MMC-222-02-10-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>MMC-222</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>MMC-222</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>The purpose of this Merchant Marine Circular is to communicate the content of 
+Resolution No. 106-62-DGMM of March 31, 2020 on the use of Merchant Marine 
+Circulars and Merchant Marine Notices. 
+3. Scope: 
+This Merchant Marine Circular goes to ship-owners, operators, managers, crew 
+agencies, ag...</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Bu Deniz Ticaret Genelgesinin amacı, Deniz Ticaret Genelgeleri ve Deniz Ticaret Bildirimlerinin kullanımına ilişkin 31 Mart 2020 tarih ve 106-62-GİGM Sayılı Kararın içeriğini duyurmaktır.    3. Kapsam: Bu Deniz Ticareti Genelgesi armatörlere, operatörlere, yöneticilere, mürettebat acentelerine ve acentalara gider.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-222-02-10-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>MMC-340-02-10-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MMC-340</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>MMC-340</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>The purpose of this Merchant Marine Circular is to communicate and offer guidance to 
+Ship-owners, Operators, Masters and Recognized Organizations on the application of the 
+new Annex 14 of the CSS Code for new and existing ships designed and fitted for the 
+carriage of containers on deck, relating ...</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesinin amacı, güvertede konteyner taşımak üzere tasarlanmış ve donatılmış yeni ve mevcut gemiler için CSS Kodunun yeni Ek 14'ünün uygulanması konusunda Gemi Sahiplerine, Operatörlere, Kaptanlara ve Tanınmış Kuruluşlara iletişim kurmak ve rehberlik sunmaktır.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-340-02-10-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>MMC-184-02-10-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MMC-184</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>MMC-184</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>The purpose of this Merchant Marine Circular is to set forth current rules and 
+regulations on Marine Accident Investigations. 
+3. 
+Scope:   
+This circular applies to the Maritime matters and Investigations of Accidents of vessels 
+flying the Panama flag. 
+4. 
+The Chapter I, Regulation 21 of...</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Bu Deniz Ticareti Genelgesinin amacı, Deniz Kazaları Soruşturmalarına ilişkin mevcut kural ve düzenlemeleri ortaya koymaktır.    3. Kapsam: Bu genelge, Panama bandıralı gemilerin denizcilik konularını ve kazalarının araştırılmasını kapsar.    4. Bölüm I, Kural 21...</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-184-02-10-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MMC-170-02-10-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MMC-170</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>MMC-170</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>The purpose of this MMC is to make known the content of the Resolution through 
+which certain guidelines of the International Maritime Organization (IMO) in relation 
+to the Night-Time Lookout – Photochromic Lenses and Dark Adaptation.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Bu MMC'nin amacı, Uluslararası Denizcilik Örgütü'nün (IMO) Gece Gözetleme - Fotokromik Lensler ve Karanlık Uyarlama ile ilgili belirli yönergelerini içeren Kararın içeriğini duyurmaktır.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-170-02-10-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>MMC-299-Sept-2023-Rv-MR.pdf</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MMC-299</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>MMC-299</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1.1. This Merchant Marine Circular supersedes MMC-38. 
+1.2. The purpose of this Circular is to inform all users that the Panamanian 
+Administration through Resolution No. 106-138-DGMM, dated 10 September 
+2013 establishes the applicable regulation to all cargo vessels of the Republic 
+of Panama un...</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesi, MMC-38'in yerine geçer.    1.2. Bu Genelgenin amacı, Panama Yönetimi'nin 10 Eylül 2013 tarih ve 106-138-GİGM sayılı Kararı ile Panama Cumhuriyeti'nin tüm kargo gemileri için geçerli düzenlemeyi oluşturduğunu tüm kullanıcılara bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-299-Sept-2023-Rv-MR sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>MMC-285-MINIMUM-SAFE-MANNING-revised-sept-2023-revoke-21-43-65-73-78-80-.pdf</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>MMC-285</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>MMC-285</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>1.1. This Merchant Marine Circular supersedes MMC-21, MMC-43, MMC-65, MMC-73, 
+MMC-78 and MMC-80.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesi, MMC-21, MMC-43, MMC-65, MMC-73, MMC-78 ve MMC-80'in yerine geçer.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-285-MINIMUM-SAFE-MANNING-revised-sept-2023-revoke-21-43-65-73-78-80- sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MMC-307-OR-CODE-Rev-MR-Sept-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MMC-307</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>MMC-307</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2.1. The purpose of this Circular is to inform about the Code for Recognized Organizations (RO 
+Code), through which all applicable requirements for recognized organizations are gathered in a 
+single IMO mandatory instrument.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2.1. Bu Genelgenin amacı, tanınmış kuruluşlar için geçerli tüm gerekliliklerin tek bir IMO zorunlu belgesinde toplandığı Tanınmış Kuruluşlar Kodu (RO Kodu) hakkında bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-307-OR-CODE-Rev-MR-Sept-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MMC-278-06-09-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>MLC, Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MMC-278</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>MMC-278</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>of this Circular is to communicate to the users of the Panamanian 
+Registry that to date, the Panama Maritime Authority has not authorized any 
+Recognized Organization to issue Certifications backing up the Recruitment and 
+Placement of Seafarers on behalf of the Republic of Panama in accordance to ...</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına bugüne kadar, Panama Denizcilik Otoritesi'nin, Panama Cumhuriyeti adına Denizcilerin İşe Alınması ve Yerleştirilmesini destekleyen Sertifikalar vermesi için herhangi bir Tanınmış Kuruluşa yetki vermediğini bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-278-06-09-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MMC-399-agosto-2023-limpio.pdf</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MMC-399</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>MMC-399</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>1.1. 
+The purpose of this Merchant Marine Circular is to inform the requirements 
+applicable to ships which are not normally engaged on international voyages 
+but which, in exceptional circumstances, are required to undertake a single 
+international voyage.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>1.1.  Bu Deniz Ticareti Genelgesinin amacı, normalde uluslararası seferlerde bulunmayan ancak istisnai durumlarda tek bir uluslararası sefer yapması gereken gemilere uygulanabilecek gereklilikleri bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-399-agosto-2023-limpio sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MMC-67-ITC69-21-de-julio-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>MMC-67</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>MMC-67</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2.1. 
+This Merchant Marine Circular is to inform to all Recognized Organizations 
+(ROs), Classification Societies, Ship-owners/Operators and other stakeholders 
+ F-33 
+  (DCCM) 
+  V.04 
+the applicability and procedures for the issuance of Tonnage Certificates to 
+Panamanian flag vessels  (IT...</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2.1.  Bu Ticari Denizcilik Genelgesi, tüm Tanınmış Kuruluşlara (RO'lar), Klas Kuruluşlarına, Gemi Sahiplerine/Operatörlere ve diğer paydaşlara F-33 (DCCM) V.04, Panama bandıralı gemilere (IT...</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-67-ITC69-21-de-julio-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MMC-283-13-06-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>MMC-283</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>MMC-283</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform to the users of the Panamanian Registry 
+about the "Guide for ship-owners or ships operators who use seafarer recruitment 
+and placement services that are based in countries or territories in which the 
+Maritime Labour Convention, 2006, as amended does not apply. Regula...</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı Panama Sicili kullanıcılarına "Denizcilik Çalışma Sözleşmesi 2006'nın tadil edildiği şekliyle geçerli olmadığı ülke veya bölgelerde bulunan denizci işe alma ve yerleştirme hizmetlerinden yararlanan gemi sahipleri veya gemi işletmecileri için Kılavuz" hakkında bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-283-13-06-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>MMC-130-24-5-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>MMC-130</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>MMC-130</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>of this Circular is to communicate to the users of the Panamanian 
+Registry, the Regulations of maritime labour inspections and the rest of the 
+provisions regarding the life, work, accommodation, food, certification and manning 
+conditions of the seafarers working on board ships of Panamanian flag,...</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına, denizcilik çalışma denetimleri Yönetmeliğini ve Panama bandıralı gemilerde çalışan denizcilerin yaşam, çalışma, barınma, beslenme, belgelendirme ve personel bulundurma koşullarına ilişkin diğer hükümleri,...</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-130-24-5-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>MMC-311-23-5-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>MMC-311</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>MMC-311</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>of this Circular is to communicate to users of the Panamanian Registry, 
+the Regulations that regulates Maritime Training Centers with head offices in the 
+Republic of Panama or abroad, headquarters and/or branches, to whom the Panama 
+Maritime Authority delegates the training of seafarers.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına, Panama Cumhuriyeti'nde veya yurtdışında merkez ofisi bulunan, Panama Denizcilik Otoritesinin denizcilerin eğitimi için yetki verdiği merkez ve/veya şubeleri bulunan Denizcilik Eğitim Merkezlerini düzenleyen Yönetmelikleri bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-311-23-5-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>MMC-351-24-5-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>MMC-351</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>MMC-351</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>of this Circular is to communicate to the users of the Panamanian 
+Registry, that this Maritime Administration implemented since June 27, 2017, the use 
+of a new stamp in the Seaman’s’ Book that is issued to seafarers, through the 
+Seafarers Automated Application System (SAA), which establishes the ...</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına, Denizcilik İdaresi'nin 27 Haziran 2017'den bu yana, Denizciler Otomatik Başvuru Sistemi (SAA) aracılığıyla denizcilere verilen Denizci Kitabında yeni bir pulun kullanımını uygulamaya koyduğunu bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-351-24-5-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>MMC-201-15-05-2023-1.pdf</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>MMC-201</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>MMC-201</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding MMC-201.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, MMC-201'e ilişkin resmi yönergeleri ve düzenleyici uyumluluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-201-15-05-2023-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>MMC-332-21-4-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>MMC-332</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>MMC-332</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>of this Circular is to communicate to the users of the Panamanian 
+Registry, the provisions for authorization as brokers of services of technical 
+documentation for seafarers.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına denizcilere yönelik teknik dokümantasyon hizmetleri komisyoncusu olarak yetki verilmesine ilişkin hükümleri bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-332-21-4-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>MMC-265-20-4-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>MMC-265</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>MMC-265</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>of this Circular is to communicate to the users of the Panamanian 
+Registry, the provisions to identify which person or category of persons may be 
+considered as “Seafarer”, and which as “Ship-owner”, for application purposes of the 
+Maritime Labour Convention, 2006, as amended (MLC, 2006, as amende...</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına, değiştirilen 2006 tarihli Denizcilik Çalışma Sözleşmesi'nin (MLC, 2006, değişiklik olarak) uygulanması amacıyla, hangi kişi veya kişi kategorisinin "Gemi Adamı" ve hangisinin "Gemi Sahibi" olarak kabul edilebileceğini belirleyen hükümleri bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-265-20-4-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>MMC-144-SEGUMAR-Apr2023-Rev-MR.pdf</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>MMC-144</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>MMC-144</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Merchant Marine Circular is to inform user regarding the full 
+implementation of the carriage of immersion suits (including the hermetically 
+packed) and anti-exposure suits on board the Panamanian flagged ships.  Also to 
+remind the shipowners, operators, and masters respon...</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesinin amacı, Panama bandıralı gemilerde daldırma giysilerinin (hermetik olarak paketlenmiş olanlar dahil) ve maruziyete karşı koruma giysilerinin taşınmasının tam olarak uygulanması konusunda kullanıcıyı bilgilendirmektir.  Ayrıca armatörlerin, operatörlerin ve kaptanların sorumluluklarını hatırlatmak isterim...</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-144-SEGUMAR-Apr2023-Rev-MR sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MMC-279-20-4-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>MMC-279</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>MMC-279</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform to the users of the Panamanian Registry that 
+once the Maritime Labour Convention, 2006, as amended (MLC, 2006, as amended) 
+comes into force on August 20, 2013; the Certificate of Inspection of Crew 
+Accommodation (CICA) shall continue to be issued to existing vessels.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına, değiştirildiği şekliyle 2006 Denizcilik Çalışma Sözleşmesi'nin (tadil edildiği şekliyle MLC, 2006) 20 Ağustos 2013 tarihinde yürürlüğe girmesiyle birlikte; Mürettebat Konaklama Denetim Sertifikası (CICA) mevcut gemilere verilmeye devam edilecektir.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-279-20-4-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>MMC-219-Rev-RB-MR-Jan-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>MMC-219</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>MMC-219</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>of providing a better service to all our users, we kindly request that 
+payments to the Segumar- Miami account, and Panama local bank account through 
+bank wire transfer (electronic payment service for transferring funds by wire), 
+include at least the following information: 
+• Name of the Ship; 
+...</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Tüm kullanıcılarımıza daha iyi bir hizmet sunabilmek amacıyla, banka havalesi yoluyla (havale yoluyla para transferi için elektronik ödeme hizmeti) Segumar-Miami hesabına ve Panama yerel banka hesabına yapılan ödemelerin en azından aşağıdaki bilgileri içermesini rica ediyoruz: • Geminin Adı;  ...</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-219-Rev-RB-MR-Jan-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>MMC-158-EPIRB-REGISTRATION-Jan-2023-Rev-MR.pdf</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>MMC-158</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>MMC-158</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>to assist States in the responsibility of beacon registration, COSPAS-
+SARSAT implemented an International 406 MHz Beacon Registration Database, allowing 
+users to register their beacons and provide information that can be of great use to SAR 
+services in the event of beacon activation. SAR services...</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Devletlere işaret ışığı kaydı sorumluluğunda yardımcı olmak için COSPAS-SARSAT, kullanıcıların kendi işaret ışıklarını kaydetmelerine ve işaret ışığının aktivasyonu durumunda SAR hizmetlerine büyük fayda sağlayabilecek bilgileri sağlamalarına olanak tanıyan bir Uluslararası 406 MHz İşaret Kayıt Veritabanını uygulamaya koymuştur. SAR hizmetleri...</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-158-EPIRB-REGISTRATION-Jan-2023-Rev-MR sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>MMC-337-15-12-2022-2.pdf</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>MMC-337</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>MMC-337</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>of this Merchant Marine Circular is to inform all the users of the Panama Registry 
+the instructions for the payment of the Continuous Synopsis Record (CSR), International Ship 
+Security Certificate (ISSC).</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi'nin amacı, Panama Sicili'nin tüm kullanıcılarına Sürekli Özet Kayıt (CSR), Uluslararası Gemi Güvenlik Sertifikası (ISSC) ödeme talimatlarını bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-337-15-12-2022-2 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MMC-384-24-10-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SMC / ISM</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>MMC-384</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>MMC-384</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>of this Merchant Marine Circular is to remind Panamanian vessel 
+companies or its representatives, about the mechanism to be used if a 
+deficiency/detention by a Port State Control Inspections is due to appeal. Additionally, 
+to provide information and guidance regarding the appeal process in the di...</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi'nin amacı, Panama gemi şirketlerine veya onların temsilcilerine, Liman Devleti Kontrol Denetimleri tarafından bir eksiklik/tutuklamanın temyiz nedeniyle olması durumunda kullanılacak mekanizmayı hatırlatmak içindir. Ayrıca, itiraz sürecine ilişkin bilgi ve rehberlik sağlamak amacıyla...</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-384-24-10-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SMS (Emniyetli Yönetim Sistemi) denetimlerinde güncelliğini kontrol edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>MMC-257-Implementation-of-EEDI-EEXI-Rev-Oct-2022-MR.pdf</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>MMC-257</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>MMC-257</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1.1. 
+2013 Guidelines for calculation of reference lines for use with the Energy Efficiency Design 
+Index (EEDI),2013 Guidelines for calculation of reference lines for use with the Energy 
+Efficiency Design Index (EEDI), The purpose of this Circular is to inform users that 2021 
+Revised MARPOL Annex...</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1.1.  2013 Enerji Verimliliği Tasarım Endeksi (EEDI) ile kullanılacak referans çizgilerinin hesaplanmasına ilişkin kılavuz, 2013 Enerji Verimliliği Tasarım Endeksi (EEDI) ile birlikte kullanılacak referans çizgilerinin hesaplanmasına ilişkin kılavuz, Bu Genelgenin amacı, 2021 Revize MARPOL Eki'nin kullanıcılara...</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-257-Implementation-of-EEDI-EEXI-Rev-Oct-2022-MR sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>MMC-121-cancelada.pdf</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>No. 121</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>121 numara</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding No. 121.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, No. 121'e ilişkin resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-121-cancelada sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>MMC-198.pdf</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>No. 198</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>198 numara</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>of this Merchant Marine Circular is to provide the guidelines to be 
+followed in order to obtain the Renewal of the Bunker Convention Certificate, taking 
+into account that the majority of the certificates, already issued, will expire on 2 
+February 2009.</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Bu Deniz Ticareti Genelgesi'nin amacı, hali hazırda verilmiş olan sertifikaların çoğunluğunun süresinin 2 Şubat 2009 tarihinde sona ereceği dikkate alınarak, Yakıt Konvansiyonu Sertifikasının Yenilenmesi için uyulması gereken esasları sağlamaktır.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-198 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>MMC-260-Rev-MR-Sept-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>MMC-260</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>MMC-260</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform shipowners and operators that our 
+Administration always aware of the global economic situation and continuously 
+committed to our policy of providing offers to our clients by creating a decrease on 
+the costs generated by our services, has deemed necessary to modify th...</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, küresel ekonomik durumun her zaman farkında olan ve hizmetlerimizden kaynaklanan maliyetlerde düşüş yaratarak müşterilerimize teklif sunma politikamıza sürekli bağlı olan İdaremizin, armatörlere ve işletmecilere, bu konuda değişiklik yapmayı gerekli gördüğü konusunda bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-260-Rev-MR-Sept-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>MMC-180-Rev-MR-Sept-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>MMC-180</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>MMC-180</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>of this Merchant Marine Circular is to inform that the Republic of Panama 
+submitted, to the Secretariat of the International Maritime Organization, the instrument 
+of accession to the Bunker Convention 2001 on 17 February 2009.</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi'nin amacı, Panama Cumhuriyeti'nin 17 Şubat 2009 tarihinde Uluslararası Denizcilik Örgütü Sekreterliğine 2001 Bunker Sözleşmesine katılım belgesini sunduğunu bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-180-Rev-MR-Sept-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>MMC-35-29-08-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>MMC-35</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>MMC-35</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform about the chartering figure under its three 
+modalities: 
+• Flagging of Foreign Ships under Bareboat Charter in Panama (OUT – IN). 
+• Ships flagged in Panama and chartered in Panama (IN–IN). 
+• Vessels flagged in Panama and chartered abroad (IN–OUT).</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, üç yöntem kapsamındaki kiralama rakamı hakkında bilgi vermektir: • Panama'da Çıplak Gemi Kiralama Kapsamında Yabancı Gemilerin Bayraklanması (OUT – IN).  • Panama bayraklı ve Panama'da (IN–IN) kiralanan gemiler.  • Panama bayraklı ve yurt dışında kiralanan gemiler (IN-OUT).</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-35-29-08-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>MMC-24-CANCELLED-SEPT-2021.pdf</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>No. 24</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>24 numara</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding No. 24.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, No. 24'e ilişkin resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-24-CANCELLED-SEPT-2021 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>MMC-277-13-06-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım, Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MMC-277</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>MMC-277</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to inform the Ship-owners/operators, legal 
+representatives of Panamanian Flagged Vessels, Panama Merchant Marine 
+Consulates and Recognized Organizations regarding the use on board of Graphical 
+symbols on Fire Control Plan and its verification. 
+1.2. Recogniz...</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Gemi Sahiplerini/İşleticilerini, Panama Bayraklı Gemilerin yasal temsilcilerini, Panama Deniz Ticaret Konsolosluklarını ve Tanınmış Kuruluşları, Yangın Kontrol Planına ilişkin Grafik sembollerin gemide kullanımı ve doğrulanması konusunda bilgilendirmektir.    1.2. Tanı...</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-277-13-06-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>MMC-336-06-06-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>MMC-336</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>MMC-336</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>The ILO adopted amendments to the Maritime Labour Convention on 11 June 2014, which 
+have the aim to improve the protection of seafarers against financial risks in possible 
+hazardous situations. For the first time, the amendments contain standards for financial 
+protection of seafarers' entitlement...</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>ILO, 11 Haziran 2014 tarihinde Denizcilik Çalışma Sözleşmesi'nde denizcilerin olası tehlikeli durumlarda mali risklere karşı korunmasını iyileştirmeyi amaçlayan değişiklikleri kabul etti. Değişiklikler ilk kez denizcilerin haklarının mali açıdan korunmasına ilişkin standartları içeriyor...</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-336-06-06-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>MMC-168-RATE-OF-DISCHARGE-OF-UNTREATED-SEWAGE-Rev.-24-05-2022-1.pdf</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>MMC-168</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>MMC-168</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to inform to all concerned parties our procedures to 
+request the approval of rate of discharge for untreated sewage.</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, arıtılmamış kanalizasyon için deşarj oranı onayı talep etme prosedürlerimizi ilgili tüm taraflara bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-168-RATE-OF-DISCHARGE-OF-UNTREATED-SEWAGE-Rev.-24-05-2022-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>MMN-304-Reference-and-contact-update-23-03-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>MMC-304</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>MMC-304</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform all users that the International Maritime 
+Organization through the Maritime Safety Committee, at its ninety-third session adopted 
+the following new traffic separation schemes and routeing measures other than traffic 
+separation schemes: 
+a. New traffic separation sc...</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, tüm kullanıcılara, Uluslararası Denizcilik Örgütü'nün, Deniz Güvenliği Komitesi aracılığıyla, doksan üçüncü oturumunda, trafik ayırım düzenleri dışında aşağıdaki yeni trafik ayırım şemalarını ve yönlendirme tedbirlerini benimsediği konusunda bilgi vermektir: a. Yeni trafik ayırma sistemi...</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>1. İlgili MMN-304-Reference-and-contact-update-23-03-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MMC-396-CICA-21-03-2022-1.pdf</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>MLC, Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>MMC-396</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>MMC-396</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform users of the Panamanian Registry, the 
+Regulation for the issuance of the Certificate of Inspection of Crew Accommodation 
+(CICA) and its exemptions, dispensations and authorizations of the Ship Registry of the 
+Republic of Panama. 
+3. The General Directorate of Seafa...</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarını, Mürettebat Konaklama Denetim Sertifikası'nın (CICA) verilmesine ilişkin Yönetmelik ve Panama Cumhuriyeti Gemi Sicili'nin muafiyetleri, muafiyetleri ve yetkileri hakkında bilgi vermektir.    3. Denizcilik Genel Müdürlüğü...</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-396-CICA-21-03-2022-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MMC-300-Oct-2014-Cancelled-17-03-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>MLC, Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>RECOGNIZED ORGANIZATIONS (RO’s)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>TANINAN KURULUŞLAR (RO'lar)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform Recognized Organizations (RO’s) that in accordance with 
+Resolution J.D. No. 011, of 2005, and for a better control and identification of vessels, the Certificate of 
+Inspection of Crew Accommodation (CICA), shall indicate also the IMO number along with the name of 
+the...</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Tanınmış Kuruluşları (RO'lar), 2005 tarihli J.D. No. 011 sayılı Karar uyarınca ve gemilerin daha iyi kontrol edilmesi ve tanımlanması için Mürettebat Konaklama Yeri Denetim Sertifikasının (CICA), geminin adıyla birlikte IMO numarasını da belirteceği konusunda bilgi vermektir...</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-300-Oct-2014-Cancelled-17-03-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>MMC-297-Sept-2014-Cancelled-17-03-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS, MLC</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators, Company Security Officers, Legal Representatives of</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Yasal Temsilciler</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform all users that Merchant Marine Circular MMC-282 
+“Maritime Labour Convention, 2006 (MLC, 2006) – Certificate of Inspection of Crew 
+Accommodation, Recreational Facilities and Food &amp; Catering.”  has been revoked and 
+therefore its content remains without effect starting ...</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, tüm kullanıcılara Ticari Denizcilik Genelgesi MMC-282 “Deniz Çalışma Sözleşmesi, 2006 (MLC, 2006) – Mürettebat Konaklama, Dinlenme Tesisleri ve Yiyecek ve İkram Denetim Sertifikası” hakkında bilgi vermektir.  iptal edildi ve bu nedenle içeriği, şu andan itibaren etkisiz kalıyor ...</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-297-Sept-2014-Cancelled-17-03-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>MMC-296-Sept-2014-Cancelled-17-03-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>MLC, Statüter / Donanım, Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>MMC-296</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>MMC-296</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>of this Circular is inform to the Recognized Organizations (OR’s) authorized to issue the 
+Certificate of Inspection of Crew Accommodation (CICA), that according with Resolution J.D. No. 011- 
+2005, the procedure to issue a dispensation or an exemption is as follows: 
+1. The Recognized Organizatio...</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin bir parçası olarak, Mürettebat Konaklama Denetim Sertifikasını (CICA) düzenlemeye yetkili Tanınmış Kuruluşlara (OR'lar), J.D. No. 011-2005 Kararına göre, muafiyet veya muafiyet verme prosedürünün aşağıdaki gibi olduğu bildirilmektedir: 1. Tanınmış Kuruluş...</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-296-Sept-2014-Cancelled-17-03-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MMC-190-Feb-2017-Cancelled-17-03-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>MLC, Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MMC-190</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>MMC-190</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>1. The purpose of this Merchant Marine Circular is to inform Owners/Operators, 
+Classifying Companies and Recognized Organizations that the Resolution of the Board 
+of Directors No. 011 of July 26th, 2005, regulates the issuance of the Certificates of 
+Inspection of Crew Accommodation (CICA).</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>1. Bu Deniz Ticareti Genelgesinin amacı, Gemi Sahiplerini/İşletmecileri, Sınıflandırma Şirketlerini ve Tanınmış Kuruluşları, 26 Temmuz 2005 tarih ve 011 sayılı Yönetim Kurulu Kararının Mürettebat Konaklama Denetim Sertifikalarının (CICA) verilmesini düzenlediği konusunda bilgilendirmektir.</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-190-Feb-2017-Cancelled-17-03-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>MMC-88-Rev.-jdg-Rev.CSG-01-02-2022.pdf</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>MMC-88</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>MMC-88</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding MMC-88.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, MMC-88'e ilişkin resmi yönergeleri ve düzenleyici uyumluluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-88-Rev.-jdg-Rev.CSG-01-02-2022 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>MMC-77-CANCELLED.pdf</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Rules and Guidelines for MOUs</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>MOU'lar için Kurallar ve Yönergeler</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding Rules and Guidelines for MOUs.</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, Mutabakat Zaptı Kuralları ve Yönergeleri ile ilgili resmi yönergeleri ve düzenleyici uyumluluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-77-CANCELLED sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>MMC-268-parrafo-4-1-4-2-14-y-16-09-12-2021.pdf</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MMC-268</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>MMC-268</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>of this Circular is to communicate users of the Panamanian Registry 
+about the adopted standard regarding watchkeeping applicable for seafarers working 
+onboard ships of Panamanian Flag, according to STCW´78 Convention, amended, the 
+MLC 2006, as amended and the national regulations.  
+3. 
+The lim...</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı Panama Sicili kullanıcılarına, değiştirilmiş STCW'78 Konvansiyonu, değiştirilmiş MLC 2006 ve ulusal düzenlemelere göre Panama Bayrağı taşıyan gemilerde çalışan denizciler için geçerli vardiya tutma ile ilgili kabul edilen standart hakkında bilgi vermektir.     3. Sınır...</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-268-parrafo-4-1-4-2-14-y-16-09-12-2021 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MMC-108-Nov-2021-Rev-MR.pdf</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>MMC-108</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>MMC-108</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>1.1 The purpose of this merchant marine circular is to inform about the publications and 
+records required on board mobile offshore units certified under the provisions of the 
+Mobile Offshore Drilling Unit Code, supply and any other ship engaged to support 
+and operate offshore.</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>1.1 Bu ticari denizcilik genelgesinin amacı, Mobil Açık Deniz Sondaj Birimi Kodu hükümlerine göre sertifikalandırılmış mobil açık deniz birimlerinde, tedarikinde ve açık denizde destek ve operasyon yapmak üzere görevlendirilen diğer gemilerde gerekli yayınlar ve kayıtlar hakkında bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-108-Nov-2021-Rev-MR sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>MMC-143-CAS-REV-MR-NOV-2021.pdf</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>MMC-143</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>MMC-143</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>1.1. 
+The Panama Maritime Authority (PMA) desires to assure that the Condition 
+Assessment Scheme (CAS), adopted by Resolution MEPC.94(46), as amended 
+and consolidated, is properly conducted by providing guidance and instructions 
+to Recognized Organizations and Shipowners.</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>1.1.  Panama Denizcilik Otoritesi (PMA), MEPC.94(46) Kararı ile kabul edilen Durum Değerlendirme Planının (CAS), tadil edilmiş ve birleştirilmiş haliyle, Tanınmış Kuruluşlara ve Gemi Sahiplerine rehberlik ve talimatlar sağlanarak uygun şekilde yürütülmesini sağlamayı arzu etmektedir.</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-143-CAS-REV-MR-NOV-2021 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>MMC-178-Rev-MR-RB-Nov-2021.pdf</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>MMC-178</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>MMC-178</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding MMC-178.</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, MMC-178'e ilişkin resmi yönergeleri ve düzenleyici uyumluluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-178-Rev-MR-RB-Nov-2021 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MMC-107-Publications-and-records-required-on-vessels-of-500-GT-Oct-2021-Rev-MR-DNSM-2.pdf</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>MMC-107</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>MMC-107</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2.1 The purpose of this merchant marine circular is to inform about the publications and 
+records required on vessels of 500 gross tonnage or above with international 
+registration in the Panamanian registry. 
+3. Publications 
+ 
+Navigational Charts appropriate for the area of navigation 
+ 
+Cor...</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2.1 Bu ticari denizcilik genelgesinin amacı, Panama sicilinde uluslararası tescile sahip 500 gros ton ve üzeri gemiler için gerekli yayınlar ve kayıtlar hakkında bilgi vermektir.    3. Yayınlar  Navigasyon alanına uygun Navigasyon Haritaları  Cor...</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-107-Publications-and-records-required-on-vessels-of-500-GT-Oct-2021-Rev-MR-DNSM-2 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MMC-394-Marine-Evacuation-System-MES-June-2021-Rev-Mr.pdf</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>MMC-394</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>MMC-394</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>1.1 
+The purpose of this Merchant Marine Circular is to provide the procedure to be 
+followed for the test of the Marine Evacuation System (MES) on Panamanian 
+registered vessels that are fitted with MES, including the requirements and 
+criteria for MES deployments.</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>1.1 Bu Ticari Denizcilik Genelgesinin amacı, MES konuşlandırmalarına ilişkin gereksinimler ve kriterler de dahil olmak üzere, MES ile donatılmış Panama kayıtlı gemilerde Deniz Tahliye Sisteminin (MES) test edilmesi için izlenecek prosedürü sağlamaktır.</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-394-Marine-Evacuation-System-MES-June-2021-Rev-Mr sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>MMC-175-16-06-2021-DGGM.pdf</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>MLC, Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>MMC-175</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>MMC-175</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>of this Circular is to communicate to the users of the Panamanian 
+Registry, that, based on Article VIII from the STCW’78 Convention, as amended, under 
+exceptional circumstances, the Panama Maritime Authority may grant a Dispensation 
+allowing a given seafarer to serve onboard ships for a determina...</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına, değiştirilmiş şekliyle STCW'78 Sözleşmesinin VIII. Maddesine dayanarak, istisnai durumlarda, Panama Denizcilik Otoritesi'nin, belirli bir denizcinin belirli bir süre için gemilerde hizmet vermesine izin veren bir Muafiyet verebileceğini bildirmektir.</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-175-16-06-2021-DGGM sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>MMC-392-IGC-Code-20-05-2021.pdf</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>MMC-392</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>MMC-392</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>. 
+1.1. The purpose of this Merchant Marine Circular is to inform Owners/Operators, 
+Recognized Organizations, Masters, and Annual Safety Inspectors on the 
+applicable procedures regarding the amendments to the IGC Code.  
+ F-33 
+  (DCCM) 
+  V.04</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>.    1.1. Bu Ticari Denizcilik Genelgesinin amacı, Gemi Sahiplerini/İşletmecileri, Tanınmış Kuruluşları, Kaptanları ve Yıllık Güvenlik Denetçilerini, IGC Kodunda yapılan değişikliklere ilişkin geçerli prosedürler konusunda bilgilendirmektir.            F-33 ​​(DCCM) V.04</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-392-IGC-Code-20-05-2021 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>MMC-389-MACN-Rev.-30-03-2021.pdf</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>MMC-389</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>MMC-389</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>The Purpose of this Merchant Marine Circular is to communicate our users that the 
+Panama Maritime Authority has joined the Maritime Anti-Corruption Network (MACN) 
+as a member with all the duties and responsibilities this involve.  The cooperation and 
+commitment of the PMA with the maritime indust...</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Bu Deniz Ticareti Genelgesinin Amacı, kullanıcılarımıza, Panama Denizcilik Otoritesi'nin, içerdiği tüm görev ve sorumluluklarla birlikte Denizcilik Yolsuzlukla Mücadele Ağı'na (MACN) üye olarak katıldığını bildirmektir.  PMA'nın denizcilik endüstrisi ile işbirliği ve bağlılığı...</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-389-MACN-Rev.-30-03-2021 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>MMC-382-PANAMA-POLICY-ON-REMOTE-SURVEY-APRIL-2021.pdf</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>MMC-382</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>MMC-382</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this circular is to inform all Recognized Organizations (RO’s) interested to 
+obtain authorization to conduct surveys and certificates on board Panama flagged 
+vessels.</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>1.1. Bu genelgenin amacı, Panama bayraklı gemilerde sörveyler ve sertifikalar yürütmek üzere yetki almak isteyen tüm Tanınmış Kuruluşları (RO'lar) bilgilendirmektir.</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-382-PANAMA-POLICY-ON-REMOTE-SURVEY-APRIL-2021 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>MMC-267-15-01-2021.pdf</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>MMC-267</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>MMC-267</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to inform users of the Panamanian Registry about 
+the issuance of Resolution No. 106-146-DGMM of December 14th., 2012 by which 
+from June 1st., 2013, all Panamanian flagged vessels of 500 GT and above, shall 
+maintain a Class Certificate onboard that certifies th...</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Panama Sicili kullanıcılarını, 1 Haziran 2013 tarihinden itibaren 500 GT ve üzeri tüm Panama bayraklı gemilerin, bu durumu tasdik eden bir Klas Sertifikasına sahip olmalarını öngören 14 Aralık 2012 tarih ve 106-146-DGMM Kararı hakkında bilgilendirmektir.</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-267-15-01-2021 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>MMC-112-03-12-2020.pdf</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS, Statüter / Donanım, Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>MMC-112</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>MMC-112</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to remind Ship-owners/Operators, Company Security 
+Officers, Legal Representatives of Panama Flagg Vessels, Panama Merchant Marine 
+Consulates and Recognized Organizations (RO’s), that the Satellite Emergency Position 
+Indicating Radio Beacon (Satellite EPIRB'S),...</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Gemi Sahipleri/İşletmecilere, Şirket Güvenlik Görevlilerine, Panama Bayraklı Gemilerin Yasal Temsilcilerine, Panama Ticari Deniz Konsolosluklarına ve Tanınmış Kuruluşlara (RO'lar), Uydu Acil Durum Konumunu Gösteren Radyo İşaretinin (Uydu EPIRB'S),...</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-112-03-12-2020 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>MMC-262-28-11-2020-DGGM.pdf</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>MMC-262</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>MMC-262</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform the users of the Panamanian Registry about 
+the minimum requirements that shall be contained in the employment agreements of 
+seafarers rendering services on board Panamanian flagged vessels engaged in 
+international navigation and other provisions relating to the seafa...</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarını, uluslararası seyrüsefer yapan Panama bandıralı gemilerde hizmet veren gemi adamlarının iş sözleşmelerinde bulunması gereken asgari şartlar ve deniz taşımacılığına ilişkin diğer hükümler hakkında bilgilendirmek...</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-262-28-11-2020-DGGM sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>MMC-387-Mandatory-Implementation-of-the-Amendments-to-the-2011-ESP-Code-Rev.-MR-2.pdf</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>MMC-387</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>MMC-387</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>1.1. This Merchant Marine Circular provides a summary of the principal aspects of the 
+guidelines for the implementation of the amendments to the International Code on 
+the Enhanced Programmed of Inspections during surveys of Bulk Carriers and Oil 
+Tankers, 2011 (2011 ESP Code) on vessels flying Pan...</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesi, Dökme Taşıyıcılar ve Petrol Tankerlerinin 2011 (2011 ESP Kodu) sörveyleri sırasında Pan'da uçan gemilerde Denetimlerin Geliştirilmiş Programlamasına İlişkin Uluslararası Kod'da yapılan değişikliklerin uygulanmasına yönelik kılavuzların temel yönlerinin bir özetini sunmaktadır.</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-387-Mandatory-Implementation-of-the-Amendments-to-the-2011-ESP-Code-Rev.-MR-2 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>MMC-375-Implmentation-sulphur-limit-Anex-VI-Nov2021.pdf</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>MMC-375</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>MMC-375</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>to communicate and facilitate smooth 
+and consistent implementation of the 0.5% Sulphur limit under MARPOL Annex VI, this 
+Administration strongly recommends to develop implementation plans, outlining how 
+the ships may prepare in order to comply with the required sulphur content limit of 
+0.50% by ...</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>MARPOL Ek VI kapsamında %0,5 Kükürt sınırının düzgün ve tutarlı bir şekilde uygulanmasını sağlamak ve kolaylaştırmak için bu İdare, gemilerin gereken %0,50 kükürt içeriği sınırına uymak için nasıl hazırlanabileceğini ana hatlarıyla belirten uygulama planlarının geliştirilmesini şiddetle tavsiye etmektedir.</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-375-Implmentation-sulphur-limit-Anex-VI-Nov2021 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>MMC-372.pdf</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>MMC-372</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>MMC-372</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Merchant Marine Circular is to provide Panamanian flagged ships on the early implementation 
+of amendment to Regulation 10 of Chapter II-2 of the International Convention for the Safety of Life at Sea 1974, 
+as amended (SOLAS), adopted on 25 November 2016, considering the MS...</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>1.1. Bu Ticari Denizcilik Genelgesinin amacı, Panama bandıralı gemilere, MS 25 Kasım 2016'da kabul edilen, değiştirildiği şekliyle (SOLAS) 1974 Uluslararası Denizde Can Güvenliği Sözleşmesinin Bölüm II-2 Kural 10'unda yapılan değişikliğin erken uygulanması hakkında bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-372 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>REV-MMC-233-September.pdf</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators, Company Security Officers, Legal</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Hukuk</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding Ship-owners/Operators, Company Security Officers, Legal.</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, Gemi Sahipleri/Operatörler, Şirket Güvenlik Görevlileri, Hukuk Görevlileri ile ilgili resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>1. İlgili REV-MMC-233-September sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>MMC-332.pdf</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>MMC-332</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>MMC-332</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>of this circular is to inform that through Official Gazette N°27987 of March 11th of 2016 entered into 
+force the Resolution J.D. N°001-2016 of February 24th of 2016: which authorize the companies and brokers, that 
+belong to the Database Program of Service Brokers of  the General Directorate of Sea...</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Bu genelgenin amacı, Denizcilik Genel Müdürlüğü Hizmet Brokerleri Veri Tabanı Programına ait şirket ve brokerları yetkilendiren 24 Şubat 2016 tarih ve J.D. N°001-2016 Kararının 11 Mart 2016 tarih ve 27987 sayılı Resmi Gazete ile yürürlüğe girdiğini bildirmektir...</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-332 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>MMC-319-FUEL-REGULATIONS-AT-BERTH-IN-HONG-KONG-SEPTEMBER-2015.pdf</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators, Company Security Officers, Legal</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Hukuk</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>of this Merchant Marine Circular is to inform the implementation of the 
+Air Pollution Control (Ocean Going Vessels) (Fuel at Berth) Regulation (LN 51 of 
+2015) by the Government of Hong Kong from 1 July 2015, which mandates ocean-
+going vessels (OGVs) to use clean fuels while berthing in Hong Kong ...</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi'nin amacı, Hong Kong Hükümeti tarafından 1 Temmuz 2015'ten itibaren okyanusa giden gemilerin (OGV'ler) Hong Kong'a yanaşırken temiz yakıt kullanmasını zorunlu kılan Hava Kirliliği Kontrolü (Okyanusa Giden Gemiler) (İskelede Yakıt) Yönetmeliğinin (LN 51, 2015) uygulanması hakkında bilgi vermektir...</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-319-FUEL-REGULATIONS-AT-BERTH-IN-HONG-KONG-SEPTEMBER-2015 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>MMC-153-30-11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>MMC-153</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>MMC-153</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>1.1. The purpose of this Circular is to communicate to the users of the Panamanian 
+Registry, the provisions about the Crew Roll Book required on board Panama 
+Flagged Vessels.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>1.1. Bu Genelgenin amacı, Panama Bayraklı Gemilerde bulunması gereken Mürettebat Kayıt Defterine ilişkin hükümleri Panama Sicili kullanıcılarına iletmektir.</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-153-30-11-2023 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>MMC-292-july2014.pdf</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators, of Panamanian Flagged Vessels, Class Societies and</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Panama Bayraklı Gemilerin, Klas Topluluklarının ve Gemi Sahipleri/İşletmecileri</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>The purpose of this Merchant Marine Circular is to revise the existing policy from Panama for 
+nondescript units. 
+2 
+Application 
+1. Nondescript Units are units other than MODUs and include all types of non-drilling units with 
+configurations as noted in the MODU Code (column-stabilized, submer...</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesinin amacı, Panama'nın sıradan birimlere yönelik mevcut politikasını revize etmektir.    2 Uygulama 1. Sıradan Olmayan Üniteler, MODU'lar dışındaki ünitelerdir ve MODU Kodunda belirtilen konfigürasyonlara sahip her türlü sondaj dışı üniteyi içerir (kolonla stabilize edilmiş, su altında...</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-292-july2014 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>MODUs-BOTTOM-SURVEY-ABR-feb-2014mmc289.pdf</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Owners/Operators of Panamanian Mobile Offshore Units, Recognized</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Panama Mobil Açık Deniz Birimlerinin Tanınmış Sahipleri/Operatörleri</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Over the years, certain types of large Mobile Offshore Drilling Units have been built and 
+certificated and they undergo the problem of cannot be handled by any existing drydocking 
+facility. Moreover, most of the time, Mobile Offshore Drilling Units are prone to exceed the due 
+date of the two dryd...</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Yıllar geçtikçe, belirli tiplerde büyük Mobil Açık Deniz Sondaj Üniteleri inşa edilmiş ve sertifikalandırılmıştır ve mevcut herhangi bir kuru havuzlama tesisi tarafından işlenememe sorunuyla karşı karşıya kalmaktadırlar. Üstelik çoğu zaman Mobil Açık Deniz Sondaj Üniteleri iki kuru sondajın son tarihini aşmaya eğilimlidir...</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>1. İlgili MODUs-BOTTOM-SURVEY-ABR-feb-2014mmc289 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>MMC-287-january2014.pdf</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators of Panamanian Flagged Vessels, Class Societies,</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Panama Bayraklı Gemilerin Armatörleri/İşletmecileri, Klas Toplulukları,</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Inform the Ship-owners/operators of Panamanian flagged vessels regarding the earlier 
+implementation of Amendment to SOLAS Reg. V/19.1 “application and requirements” related to the 
+provision of BNWAS to ships constructed before 1st July 2002. 
+2 
+Application 
+Since 1st January 2011 the carriage...</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Panama bandıralı gemilerin armatörlerini/işletmecilerini SOLAS Reg. 1 Temmuz 2002'den önce inşa edilen gemilere BNWAS sağlanmasına ilişkin V/19.1 “uygulama ve gereklilikler”. 2 Uygulama 1 Ocak 2011'den bu yana taşıma...</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-287-january2014 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>MMC-266-Notification-Consulado-de-Turqu-Julio-2015.pdf</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators, Company Security Officers, Legal</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Hukuk</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>of this Circular is to inform users of the Panamanian Registry that our 
+Administration, always committed to the continuous improvement, deemed necessary to 
+provide consular services within the Republic of Turkey and has therefore, granted through 
+Resolution J.D. No. 053-2012, the category of Merc...</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Bu Genelgenin amacı, Panama Sicili kullanıcılarına, her zaman sürekli iyileştirmeyi taahhüt eden İdaremizin, Türkiye Cumhuriyeti'nde konsolosluk hizmetleri sağlamayı gerekli gördüğü ve bu nedenle J.D. No. 053-2012 Kararı ile Merc...</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-266-Notification-Consulado-de-Turqu-Julio-2015 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>232.pdf</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators, Company Security Officers, Legal Representatives of</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Yasal Temsilciler</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding Ship-owners/Operators, Company Security Officers, Legal Representatives of.</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, Gemi Sahipleri/Operatörleri, Şirket Güvenlik Görevlileri ve Yasal Temsilcilerine ilişkin resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>1. İlgili 232 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>018.pdf</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators, Company Security Officers, Legal Representatives of</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Yasal Temsilciler</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding Ship-owners/Operators, Company Security Officers, Legal Representatives of.</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, Gemi Sahipleri/Operatörleri, Şirket Güvenlik Görevlileri ve Yasal Temsilcilerine ilişkin resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>1. İlgili 018 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>060.pdf</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Shipowners/Operators, Company Security Officers, Legal Representatives of</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Yasal Temsilciler</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding Shipowners/Operators, Company Security Officers, Legal Representatives of.</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, Gemi Sahipleri/Operatörleri, Şirket Güvenlik Görevlileri ve Yasal Temsilcileri ile ilgili resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>1. İlgili 060 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>017.pdf</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS, Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators, Company Security Officers, Legal Representatives</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Yasal Temsilciler</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>of this circular is to provide you with information related to the Application for 
+Radiocommunication Station License in the Maritime Mobile Service.</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Bu genelgenin amacı, Deniz Mobil Hizmetinde Telsiz Haberleşme İstasyon Lisansı Başvurusu ile ilgili olarak tarafınıza bilgi vermektir.</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>1. İlgili 017 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>009.pdf</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Shipowners/Operators, Company Security Officers, Legal Representatives of</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Yasal Temsilciler</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding Shipowners/Operators, Company Security Officers, Legal Representatives of.</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, Gemi Sahipleri/Operatörleri, Şirket Güvenlik Görevlileri ve Yasal Temsilcileri ile ilgili resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>1. İlgili 009 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>008.pdf</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators, Company Security Officers, Legal        Representatives of</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Yasal Temsilciler</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding Ship-owners/Operators, Company Security Officers, Legal        Representatives of.</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, Gemi Sahipleri/Operatörleri, Şirket Güvenlik Görevlileri ve Yasal Temsilcilerine ilişkin resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>1. İlgili 008 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>011.pdf</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators, Company Security Officers, Legal Representatives of</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Yasal Temsilciler</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding Ship-owners/Operators, Company Security Officers, Legal Representatives of.</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, Gemi Sahipleri/Operatörleri, Şirket Güvenlik Görevlileri ve Yasal Temsilcilerine ilişkin resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>1. İlgili 011 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>012.pdf</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Shipowners/Operators, Company Security Officers, Legal Representatives of</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Yasal Temsilciler</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding Shipowners/Operators, Company Security Officers, Legal Representatives of.</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, Gemi Sahipleri/Operatörleri, Şirket Güvenlik Görevlileri ve Yasal Temsilcileri ile ilgili resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>1. İlgili 012 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>016.pdf</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ISSC / ISPS</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Shipowners/Operators, Company Security Officers, Legal Representatives of</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Yasal Temsilciler</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding Shipowners/Operators, Company Security Officers, Legal Representatives of.</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, Gemi Sahipleri/Operatörleri, Şirket Güvenlik Görevlileri ve Yasal Temsilcileri ile ilgili resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>1. İlgili 016 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SSP (Gemi Güvenlik Planı) ve SSAS ayarlarını bu genelgeye göre revize edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>MMC-227-JULY-2011-CANCELLED-JUNE-2021.pdf</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>MLC</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>MMC-227</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>MMC-227</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>of this circular is to inform users about the current stage of the adaptation of the 
+national regulation according to the requirements of   the   Maritime   Labour   Convention, 
+2006, (MLC, 2006) as well as the issuance of the Declaration of the Maritime Labour 
+Compliance - Part I".</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Bu genelgenin amacı, ulusal mevzuatın Denizcilik Çalışma Sözleşmesi, 2006 (MLC, 2006) gerekliliklerine göre uyarlanmasının mevcut aşaması ve Denizcilik Çalışma Uygunluğu Bildirgesi - Bölüm I'in yayımlanması hakkında kullanıcıları bilgilendirmektir.</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-227-JULY-2011-CANCELLED-JUNE-2021 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. Gemiadamı iş sözleşmeleri ve dinlenme saatleri planlamalarında bu genelge kurallarını göz önünde bulundurun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>MMC-213-1-1.pdf</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>SMC / ISM, ISSC / ISPS, Klas / RO Yetkileri</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Ship-owners/Operators, Company Security Officers, Legal</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Armatörler/Operatörler, Şirket Güvenlik Görevlileri, Hukuk</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>to insure proper and common implementation of such requirement, this 
+Administration instructs all duly approved Recognized Organizations to issue ISM 
+certification on behalf of the Republic of Panama to use the above mentioned 
+guidance when verifying compliance with the clause 1.2.2.2 of the ISM ...</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Bu gerekliliğin düzgün ve ortak bir şekilde uygulanmasını sağlamak için, bu İdare, usulüne uygun olarak onaylanmış tüm Tanınmış Kuruluşlara, ISM'nin 1.2.2.2 maddesine uygunluğu doğrularken yukarıda belirtilen kılavuzu kullanmak üzere Panama Cumhuriyeti adına ISM sertifikası düzenlemeleri talimatını verir.</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-213-1-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SMS (Emniyetli Yönetim Sistemi) denetimlerinde güncelliğini kontrol edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>210.pdf</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Owners, Operators, Masters of Panama flag vessels, Consular Offices, Law</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Panama bandıralı gemilerin sahipleri, işletmecileri, kaptanları, Konsolosluk Büroları, Hukuk</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>s:  
+a) 
+Inclusion of a definition of  fishing support vessel and fishing related activities;  
+b) 
+Clarify that transshipment at high seas is not forbidden but regulated; 
+PANAMA MARITIME AUTHORITY 
+MERCHANT MARINE CIRCULAR MMC-210 
+PanCanal Building  
+Albrook, Panama City 
+Republic of Panama...</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>a) Balıkçılık destek gemisi ve balıkçılıkla ilgili faaliyetlerin tanımının dahil edilmesi;   b) Açık denizlerde aktarmanın yasak olmayıp düzenlendiğini açıklığa kavuşturun;      PANAMA DENİZCİLİK YETKİSİ TİCARİ DENİZ GENELGESİ MMC-210 PanCanal Binası Albrook, Panama Şehri Panama Cumhuriyeti...</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>1. İlgili 210 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>115-Cancelled-1.pdf</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>SMC / ISM</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>No. 115</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>115 numara</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>of this Merchant Marine Circular is to remind shipowners/operators and masters of Panamanian registered ships of the full implementation of The 
+International Management Code for the Safe Operation of Ships and for Pollution Prevention (ISM Code). This Code became mandatory for certain ships as from...</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi'nin amacı, Panama tescilli gemilerin armatörleri/operatörleri ve kaptanlarına, Gemilerin Güvenli Kullanımı ve Kirliliğin Önlenmesi için Uluslararası Yönetim Kodunun (ISM Kodu) tam olarak uygulandığını hatırlatmak içindir. Bu Kurallar, belirli gemiler için zorunlu hale geldi...</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>1. İlgili 115-Cancelled-1 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin. 3. SMS (Emniyetli Yönetim Sistemi) denetimlerinde güncelliğini kontrol edin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>114.pdf</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Genel / Diğer</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>No. 114</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>114 numara</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>This Merchant Marine Circular details the official guidelines and regulatory compliance requirements regarding No. 114.</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Bu Ticari Denizcilik Genelgesi, No. 114'e ilişkin resmi yönergeleri ve mevzuata uygunluk gerekliliklerini ayrıntılı olarak açıklamaktadır.</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>1. İlgili 114 sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>MMC-383-RO-GBS-Rev-MR-RJ.pdf</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Statüter / Donanım</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>MMC-383</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>MMC-383</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Merchant Marine Circular</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>1.1. The propose of this circular is to inform the list of organizations recognized by 
+administrations in accordance with the provisions of SOLAS regulation XI-1/1, 
+whose rules have been confirmed as conforming to the GBS, as per 
+MSC.1/Circ.1518/Rev.1, dated on December 4, 2018, as amended. 
+ F...</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>1.1. Bu genelgenin amacı, 4 Aralık 2018 tarihli MSC.1/Circ.1518/Rev.1 uyarınca kurallarının GBS'ye uygun olduğu teyit edilen SOLAS yönetmeliği XI-1/1 hükümleri uyarınca idareler tarafından tanınan kuruluşların listesinin güncel olarak bilgilendirilmesidir.     F...</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>1. İlgili MMC-383-RO-GBS-Rev-MR-RJ sayılı genelgeyi gemideki sirküler klasörüne ekleyin. 2. Genelgede belirtilen teknik ve operasyonel şartları PSC denetimleri öncesinde kontrol listesine ekleyin.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
